--- a/Fase 3/Evidencias Proyecto/Evidencias de documentación/PLANILLA SET DE PRUEBAS.xlsx
+++ b/Fase 3/Evidencias Proyecto/Evidencias de documentación/PLANILLA SET DE PRUEBAS.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="419">
   <si>
     <t>NOMBRE TESTING</t>
   </si>
@@ -238,144 +238,216 @@
     <t>USUARIOS RELACIONADOS:  Cliente</t>
   </si>
   <si>
+    <t>P-02-001</t>
+  </si>
+  <si>
     <t>Agregar Productos</t>
   </si>
   <si>
     <t>El producto se muestra en el carrito con toda la información correcta (nombre, imagen, precio, cantidad y subtotal).</t>
   </si>
   <si>
+    <t>P-02-002</t>
+  </si>
+  <si>
     <t>Actualizar cantidad</t>
   </si>
   <si>
     <t>El carrito actualiza los datos cambiados con el subtotal correspondiente.</t>
   </si>
   <si>
+    <t>P-02-003</t>
+  </si>
+  <si>
     <t>Eliminar productos</t>
   </si>
   <si>
     <t>El producto desaparece del carrito y el total se actualiza correctamente.</t>
   </si>
   <si>
+    <t>P-02-004</t>
+  </si>
+  <si>
     <t>Visualización del carrito</t>
   </si>
   <si>
     <t>Se visualizan correctamente todas las actualizaciones y el botón de checkout.</t>
   </si>
   <si>
+    <t>P-02-005</t>
+  </si>
+  <si>
     <t>Visualización de productos en el carrito</t>
   </si>
   <si>
     <t>Todos los productos se muestran con su información completa y correcta.</t>
   </si>
   <si>
+    <t>P-02-006</t>
+  </si>
+  <si>
     <t>Evitar duplicados</t>
   </si>
   <si>
     <t>El carrito muestra una sola línea del producto con la cantidad actualizada.</t>
   </si>
   <si>
+    <t>P-02-007</t>
+  </si>
+  <si>
     <t>Carrito vacío</t>
   </si>
   <si>
     <t>Se muestra el mensaje “Tu carrito está vacío” y la opción “Volver a la tienda”.</t>
   </si>
   <si>
+    <t>P-02-008</t>
+  </si>
+  <si>
     <t>Cálculo de totales</t>
   </si>
   <si>
     <t>El total general es la suma correcta de subtotales + envío (si aplica).</t>
   </si>
   <si>
+    <t>P-02-009</t>
+  </si>
+  <si>
     <t>Validación de stock</t>
   </si>
   <si>
     <t>El sistema no permite agregar más productos que el stock actual disponible.</t>
   </si>
   <si>
+    <t>P-02-010</t>
+  </si>
+  <si>
     <t>Acceso a checkout</t>
   </si>
   <si>
     <t>El sistema muestra mensaje “Tu carrito está vacío” y la opción “Volver a la tienda” al intentar checkout sin productos.</t>
   </si>
   <si>
+    <t>P-02-011</t>
+  </si>
+  <si>
     <t>Checkout básico valido</t>
   </si>
   <si>
     <t>El sistema registra los datos del usuario en la base de datos y envía el correo con resumen de compra.</t>
   </si>
   <si>
+    <t>P-02-012</t>
+  </si>
+  <si>
     <t xml:space="preserve">Checkout con datos invalidos </t>
   </si>
   <si>
     <t xml:space="preserve">El sistema muestra un mensaje de error indicando qué datos corregir y retrocede la validación. </t>
   </si>
   <si>
+    <t>P-02-013</t>
+  </si>
+  <si>
     <t>Validación de campos</t>
   </si>
   <si>
     <t>El sistema no permite avanzar sin rellenar los campos obligatorios.</t>
   </si>
   <si>
+    <t>P-02-014</t>
+  </si>
+  <si>
     <t>Selección de método de pago</t>
   </si>
   <si>
     <t>El flujo es continuo al paso siguiente sin errores ni pérdida de datos ingresados.</t>
   </si>
   <si>
+    <t>P-02-015</t>
+  </si>
+  <si>
     <t>Metodo de pago exito</t>
   </si>
   <si>
     <t>El pago se procesó exitosamente, se generó el pedido en la base de datos y se envió el correo de confirmación.</t>
   </si>
   <si>
+    <t>P-02-016</t>
+  </si>
+  <si>
     <t>Metodo de pago rechazado</t>
   </si>
   <si>
     <t>El sistema detectó tarjeta inválida y mostró mensaje en pantalla: "Datos de tarjeta incorrectos". No se generó pedido.</t>
   </si>
   <si>
+    <t>P-02-017</t>
+  </si>
+  <si>
     <t>Pago con fondos insuficientes</t>
   </si>
   <si>
     <t>El sistema no genero ningún pedido por pago con falta de fondos.</t>
   </si>
   <si>
+    <t>P-02-018</t>
+  </si>
+  <si>
     <t>Cancelación durante el pago</t>
   </si>
   <si>
     <t>No se realia la vemta y el producto sigue en el carrito.</t>
   </si>
   <si>
+    <t>P-02-019</t>
+  </si>
+  <si>
     <t>Registro de pedido en base de datos</t>
   </si>
   <si>
     <t>Se guarda en la base de datos con ID y con estado inicial "Pendiente".</t>
   </si>
   <si>
+    <t>P-02-020</t>
+  </si>
+  <si>
     <t>Vaciar carrito tras compra</t>
   </si>
   <si>
     <t>Tras confirmar la compra, automáticamente el carrito se vacía y vuelve al inicio</t>
   </si>
   <si>
+    <t>P-02-021</t>
+  </si>
+  <si>
     <t>Envío de correo de confirmación de compra</t>
   </si>
   <si>
     <t>El sistema detalla que fue enviado el correo y se verifica en la recepción de bandeja del usuario.</t>
   </si>
   <si>
+    <t>P-02-022</t>
+  </si>
+  <si>
     <t>Carrito con sesión de invitado</t>
   </si>
   <si>
     <t>El usuario mantiene su carrito normal para poder realizar su checkout.</t>
   </si>
   <si>
+    <t>P-02-023</t>
+  </si>
+  <si>
     <t>Mensaje de confirmación visual en pantalla</t>
   </si>
   <si>
     <t>El pago es exitoso, la web mostró un mensaje grande y claro: “¡Compra realizada con éxito!”.</t>
   </si>
   <si>
+    <t>P-02-024</t>
+  </si>
+  <si>
     <t>Cálculo de costos de envío</t>
   </si>
   <si>
@@ -391,82 +463,127 @@
     <t xml:space="preserve">USUARIOS RELACIONADOS:  Administrador </t>
   </si>
   <si>
+    <t>P-03-001</t>
+  </si>
+  <si>
     <t>Lectura de producto</t>
   </si>
   <si>
     <t>Se muestra la información correspondiente y actualizada.</t>
   </si>
   <si>
+    <t>P-03-002</t>
+  </si>
+  <si>
     <t>Creacion de productos con datos correctos</t>
   </si>
   <si>
     <t>Se registra los datos en la tabla de productos.</t>
   </si>
   <si>
+    <t>P-03-003</t>
+  </si>
+  <si>
     <t>Actualizar cantidad con datos correctos</t>
   </si>
   <si>
     <t>La base de datos proyecta los nuevos stock y datos actualizados.</t>
   </si>
   <si>
+    <t>P-03-004</t>
+  </si>
+  <si>
     <t>Actualizar con datos incorrectos</t>
   </si>
   <si>
     <t>El sistema rechaza los cambios por no ser datos positivos.</t>
   </si>
   <si>
+    <t>P-03-005</t>
+  </si>
+  <si>
     <t>Actualizar productos con datos faltantes</t>
   </si>
   <si>
     <t>No se realizan la actualizacion por falta de datos asignados.</t>
   </si>
   <si>
+    <t>P-03-006</t>
+  </si>
+  <si>
     <t>Refleja un mensaje de seguridad ya que se elimina por completo del panel y base de datos.</t>
   </si>
   <si>
+    <t>P-03-007</t>
+  </si>
+  <si>
     <t>Creación de producto con campos vacios</t>
   </si>
   <si>
     <t>No se generan los productos si no cumple con los campos asignados de informacion y no se registran.</t>
   </si>
   <si>
+    <t>P-03-008</t>
+  </si>
+  <si>
     <t>Creacion con producto duplicado</t>
   </si>
   <si>
     <t>No genera el nuevo producto por existencia similar de ID.</t>
   </si>
   <si>
+    <t>P-03-009</t>
+  </si>
+  <si>
     <t>Validación de precios</t>
   </si>
   <si>
     <t>El sistema arroja un error por valores inválidos y no le permite continuar.</t>
   </si>
   <si>
+    <t>P-03-010</t>
+  </si>
+  <si>
     <t>El sistema muestra un mensaje de "Stock debe ser número entero" y no guarda valores negativos.</t>
   </si>
   <si>
+    <t>P-03-011</t>
+  </si>
+  <si>
     <t>Carga de imágenes</t>
   </si>
   <si>
     <t>La imagen se cargó correctamente y se visualiza en el panel y en el producto</t>
   </si>
   <si>
+    <t>P-03-012</t>
+  </si>
+  <si>
     <t>Editar actualizar datos de productos con datos correctos</t>
   </si>
   <si>
     <t>En el panel se reflejan la actualización y tambien en la base de datos.</t>
   </si>
   <si>
+    <t>P-03-013</t>
+  </si>
+  <si>
     <t>Editar y actualizar datos de producto con datos incorrectos</t>
   </si>
   <si>
     <t>El sistema arroja un error poque no cumple con datos correctos.</t>
   </si>
   <si>
+    <t>P-03-014</t>
+  </si>
+  <si>
     <t>Actualización de campos protegidos</t>
   </si>
   <si>
     <t>Los campos ID y fecha_creación aparecieron deshabilitados y no editables.</t>
+  </si>
+  <si>
+    <t>P-03-015</t>
   </si>
   <si>
     <t xml:space="preserve">Mensajes errores, confirmaciones o eliminación de producto </t>
@@ -1531,7 +1648,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="80">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1585,6 +1702,7 @@
     <xf borderId="8" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="11" fillId="0" fontId="7" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -1593,8 +1711,6 @@
     <xf borderId="8" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1614,17 +1730,14 @@
     <xf borderId="3" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
+    <xf borderId="8" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="8" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="8" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="11" fillId="0" fontId="7" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="8" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
@@ -1632,7 +1745,6 @@
     <xf borderId="8" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="8" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -1642,10 +1754,9 @@
     <xf borderId="8" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="8" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="11" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
@@ -1672,10 +1783,6 @@
     <xf borderId="8" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="12" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="8" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -1685,6 +1792,7 @@
     <xf borderId="12" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="16" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -1696,6 +1804,9 @@
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="8" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1745,9 +1856,6 @@
     </xf>
     <xf borderId="0" fillId="3" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -2086,10 +2194,10 @@
         <v>18</v>
       </c>
       <c r="D8" s="20"/>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="21">
+      <c r="F8" s="22">
         <v>0.883</v>
       </c>
     </row>
@@ -2104,26 +2212,26 @@
         <v>18</v>
       </c>
       <c r="D9" s="20"/>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="22"/>
+      <c r="F9" s="23"/>
     </row>
     <row r="10">
       <c r="A10" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="24" t="s">
         <v>24</v>
       </c>
       <c r="C10" s="19"/>
       <c r="D10" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="22"/>
+      <c r="F10" s="23"/>
     </row>
     <row r="11">
       <c r="A11" s="17" t="s">
@@ -2132,14 +2240,14 @@
       <c r="B11" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="25" t="s">
         <v>18</v>
       </c>
       <c r="D11" s="20"/>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="F11" s="22"/>
+      <c r="F11" s="23"/>
     </row>
     <row r="12">
       <c r="A12" s="17" t="s">
@@ -2152,10 +2260,10 @@
         <v>18</v>
       </c>
       <c r="D12" s="20"/>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="22"/>
+      <c r="F12" s="23"/>
     </row>
     <row r="13">
       <c r="A13" s="17" t="s">
@@ -2168,10 +2276,10 @@
         <v>18</v>
       </c>
       <c r="D13" s="20"/>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="F13" s="22"/>
+      <c r="F13" s="23"/>
     </row>
     <row r="14">
       <c r="A14" s="17" t="s">
@@ -2184,10 +2292,10 @@
         <v>18</v>
       </c>
       <c r="D14" s="20"/>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="F14" s="22"/>
+      <c r="F14" s="23"/>
     </row>
     <row r="15">
       <c r="A15" s="17" t="s">
@@ -2203,7 +2311,7 @@
       <c r="E15" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="F15" s="22"/>
+      <c r="F15" s="23"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="s">
@@ -2216,10 +2324,10 @@
         <v>18</v>
       </c>
       <c r="D16" s="20"/>
-      <c r="E16" s="25" t="s">
+      <c r="E16" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="F16" s="22"/>
+      <c r="F16" s="23"/>
     </row>
     <row r="17">
       <c r="A17" s="17" t="s">
@@ -2228,149 +2336,149 @@
       <c r="B17" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="C17" s="25" t="s">
         <v>18</v>
       </c>
       <c r="D17" s="20"/>
       <c r="E17" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="F17" s="22"/>
+      <c r="F17" s="23"/>
     </row>
     <row r="18">
       <c r="A18" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="26" t="s">
+      <c r="B18" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="27" t="s">
+      <c r="C18" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="27"/>
-      <c r="E18" s="1" t="s">
+      <c r="D18" s="26"/>
+      <c r="E18" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="F18" s="22"/>
+      <c r="F18" s="23"/>
     </row>
     <row r="19">
       <c r="A19" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="26" t="s">
+      <c r="B19" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="27" t="s">
+      <c r="C19" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="27"/>
-      <c r="E19" s="1" t="s">
+      <c r="D19" s="26"/>
+      <c r="E19" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="F19" s="22"/>
+      <c r="F19" s="23"/>
     </row>
     <row r="20">
       <c r="A20" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="B20" s="26" t="s">
+      <c r="B20" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="C20" s="27" t="s">
+      <c r="C20" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="27"/>
-      <c r="E20" s="1" t="s">
+      <c r="D20" s="26"/>
+      <c r="E20" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="F20" s="22"/>
+      <c r="F20" s="23"/>
     </row>
     <row r="21">
       <c r="A21" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="B21" s="26" t="s">
+      <c r="B21" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="C21" s="27" t="s">
+      <c r="C21" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="D21" s="27"/>
-      <c r="E21" s="26" t="s">
+      <c r="D21" s="26"/>
+      <c r="E21" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="F21" s="22"/>
+      <c r="F21" s="23"/>
     </row>
     <row r="22">
       <c r="A22" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="B22" s="26" t="s">
+      <c r="B22" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="C22" s="27" t="s">
+      <c r="C22" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="27"/>
-      <c r="E22" s="26" t="s">
+      <c r="D22" s="26"/>
+      <c r="E22" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="F22" s="22"/>
+      <c r="F22" s="23"/>
     </row>
     <row r="23">
       <c r="A23" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="B23" s="26" t="s">
+      <c r="B23" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27" t="s">
+      <c r="C23" s="26"/>
+      <c r="D23" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="E23" s="26" t="s">
+      <c r="E23" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="F23" s="22"/>
+      <c r="F23" s="23"/>
     </row>
     <row r="24">
       <c r="A24" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="B24" s="26" t="s">
+      <c r="B24" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="C24" s="27" t="s">
+      <c r="C24" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="D24" s="27"/>
-      <c r="E24" s="26" t="s">
+      <c r="D24" s="26"/>
+      <c r="E24" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="F24" s="28"/>
+      <c r="F24" s="27"/>
     </row>
     <row r="25">
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
     </row>
     <row r="26">
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
     </row>
     <row r="27">
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B28" s="30" t="s">
+      <c r="B28" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
@@ -2379,38 +2487,38 @@
       <c r="B29" s="4">
         <v>45950.0</v>
       </c>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B30" s="31">
+      <c r="B30" s="30">
         <v>0.75</v>
       </c>
-      <c r="C30" s="29"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B31" s="32">
+      <c r="B31" s="31">
         <v>0.9166666666666666</v>
       </c>
-      <c r="C31" s="29"/>
-      <c r="D31" s="29"/>
-      <c r="E31" s="29"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="s">
         <v>70</v>
       </c>
       <c r="B32" s="7"/>
-      <c r="C32" s="33" t="s">
+      <c r="C32" s="32" t="s">
         <v>7</v>
       </c>
       <c r="D32" s="9"/>
@@ -2448,349 +2556,397 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="17"/>
+      <c r="A35" s="33" t="s">
+        <v>72</v>
+      </c>
       <c r="B35" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="C35" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C35" s="25" t="s">
         <v>18</v>
       </c>
       <c r="D35" s="19"/>
       <c r="E35" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="F35" s="36">
-        <v>0.7</v>
+        <v>74</v>
+      </c>
+      <c r="F35" s="22">
+        <v>1.0</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="37"/>
+      <c r="A36" s="33" t="s">
+        <v>75</v>
+      </c>
       <c r="B36" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="C36" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="C36" s="25" t="s">
         <v>18</v>
       </c>
       <c r="D36" s="19"/>
       <c r="E36" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="F36" s="22"/>
+        <v>77</v>
+      </c>
+      <c r="F36" s="23"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="37"/>
+      <c r="A37" s="33" t="s">
+        <v>78</v>
+      </c>
       <c r="B37" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="C37" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="C37" s="25" t="s">
         <v>18</v>
       </c>
       <c r="D37" s="19"/>
       <c r="E37" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="F37" s="22"/>
+        <v>80</v>
+      </c>
+      <c r="F37" s="23"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="37"/>
+      <c r="A38" s="33" t="s">
+        <v>81</v>
+      </c>
       <c r="B38" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="C38" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="C38" s="25" t="s">
         <v>18</v>
       </c>
       <c r="D38" s="19"/>
       <c r="E38" s="35" t="s">
-        <v>79</v>
-      </c>
-      <c r="F38" s="22"/>
+        <v>83</v>
+      </c>
+      <c r="F38" s="23"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="37"/>
-      <c r="B39" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="C39" s="24" t="s">
+      <c r="A39" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="B39" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="C39" s="25" t="s">
         <v>18</v>
       </c>
       <c r="D39" s="19"/>
       <c r="E39" s="35" t="s">
-        <v>81</v>
-      </c>
-      <c r="F39" s="22"/>
+        <v>86</v>
+      </c>
+      <c r="F39" s="23"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="37"/>
-      <c r="B40" s="38" t="s">
-        <v>82</v>
-      </c>
-      <c r="C40" s="24" t="s">
+      <c r="A40" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="B40" s="36" t="s">
+        <v>88</v>
+      </c>
+      <c r="C40" s="25" t="s">
         <v>18</v>
       </c>
       <c r="D40" s="19"/>
       <c r="E40" s="35" t="s">
-        <v>83</v>
-      </c>
-      <c r="F40" s="22"/>
+        <v>89</v>
+      </c>
+      <c r="F40" s="23"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="37"/>
-      <c r="B41" s="38" t="s">
-        <v>84</v>
-      </c>
-      <c r="C41" s="24" t="s">
+      <c r="A41" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="B41" s="36" t="s">
+        <v>91</v>
+      </c>
+      <c r="C41" s="25" t="s">
         <v>18</v>
       </c>
       <c r="D41" s="19"/>
       <c r="E41" s="35" t="s">
-        <v>85</v>
-      </c>
-      <c r="F41" s="22"/>
+        <v>92</v>
+      </c>
+      <c r="F41" s="23"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="37"/>
-      <c r="B42" s="38" t="s">
-        <v>86</v>
-      </c>
-      <c r="C42" s="24" t="s">
+      <c r="A42" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="B42" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="C42" s="25" t="s">
         <v>18</v>
       </c>
       <c r="D42" s="19"/>
       <c r="E42" s="35" t="s">
-        <v>87</v>
-      </c>
-      <c r="F42" s="22"/>
+        <v>95</v>
+      </c>
+      <c r="F42" s="23"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="37"/>
-      <c r="B43" s="38" t="s">
-        <v>88</v>
-      </c>
-      <c r="C43" s="24" t="s">
+      <c r="A43" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="B43" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="C43" s="25" t="s">
         <v>18</v>
       </c>
       <c r="D43" s="19"/>
       <c r="E43" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="F43" s="22"/>
+        <v>98</v>
+      </c>
+      <c r="F43" s="23"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="37"/>
-      <c r="B44" s="38" t="s">
-        <v>90</v>
-      </c>
-      <c r="C44" s="24" t="s">
+      <c r="A44" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="B44" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="C44" s="25" t="s">
         <v>18</v>
       </c>
       <c r="D44" s="19"/>
       <c r="E44" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="F44" s="22"/>
+        <v>101</v>
+      </c>
+      <c r="F44" s="23"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="37"/>
+      <c r="A45" s="33" t="s">
+        <v>102</v>
+      </c>
       <c r="B45" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="C45" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="C45" s="25" t="s">
         <v>18</v>
       </c>
       <c r="D45" s="19"/>
       <c r="E45" s="35" t="s">
-        <v>93</v>
-      </c>
-      <c r="F45" s="28"/>
+        <v>104</v>
+      </c>
+      <c r="F45" s="23"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="26"/>
+      <c r="A46" s="33" t="s">
+        <v>105</v>
+      </c>
       <c r="B46" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="C46" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="C46" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D46" s="39"/>
+      <c r="D46" s="37"/>
       <c r="E46" s="35" t="s">
-        <v>95</v>
-      </c>
-      <c r="F46" s="40"/>
+        <v>107</v>
+      </c>
+      <c r="F46" s="23"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="26"/>
+      <c r="A47" s="33" t="s">
+        <v>108</v>
+      </c>
       <c r="B47" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="C47" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="C47" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D47" s="39"/>
+      <c r="D47" s="37"/>
       <c r="E47" s="35" t="s">
-        <v>97</v>
-      </c>
-      <c r="F47" s="1"/>
+        <v>110</v>
+      </c>
+      <c r="F47" s="23"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="26"/>
+      <c r="A48" s="33" t="s">
+        <v>111</v>
+      </c>
       <c r="B48" s="34" t="s">
-        <v>98</v>
-      </c>
-      <c r="C48" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="C48" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D48" s="39"/>
+      <c r="D48" s="37"/>
       <c r="E48" s="35" t="s">
-        <v>99</v>
-      </c>
-      <c r="F48" s="1"/>
+        <v>113</v>
+      </c>
+      <c r="F48" s="23"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="26"/>
+      <c r="A49" s="33" t="s">
+        <v>114</v>
+      </c>
       <c r="B49" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="C49" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="C49" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D49" s="39"/>
+      <c r="D49" s="37"/>
       <c r="E49" s="35" t="s">
-        <v>101</v>
-      </c>
-      <c r="F49" s="1"/>
+        <v>116</v>
+      </c>
+      <c r="F49" s="23"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="26"/>
+      <c r="A50" s="33" t="s">
+        <v>117</v>
+      </c>
       <c r="B50" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="C50" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="C50" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D50" s="39"/>
+      <c r="D50" s="37"/>
       <c r="E50" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="F50" s="1"/>
+        <v>119</v>
+      </c>
+      <c r="F50" s="23"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="26"/>
+      <c r="A51" s="33" t="s">
+        <v>120</v>
+      </c>
       <c r="B51" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="C51" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="C51" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D51" s="39"/>
-      <c r="E51" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="F51" s="1"/>
+      <c r="D51" s="37"/>
+      <c r="E51" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="F51" s="23"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="26"/>
+      <c r="A52" s="33" t="s">
+        <v>123</v>
+      </c>
       <c r="B52" s="34" t="s">
-        <v>106</v>
-      </c>
-      <c r="C52" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="C52" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D52" s="39"/>
-      <c r="E52" s="42" t="s">
-        <v>107</v>
-      </c>
-      <c r="F52" s="1"/>
+      <c r="D52" s="37"/>
+      <c r="E52" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="F52" s="23"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="26"/>
+      <c r="A53" s="33" t="s">
+        <v>126</v>
+      </c>
       <c r="B53" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="C53" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="C53" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D53" s="39"/>
-      <c r="E53" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="F53" s="1"/>
+      <c r="D53" s="37"/>
+      <c r="E53" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="F53" s="23"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="26"/>
-      <c r="B54" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="C54" s="24" t="s">
+      <c r="A54" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="B54" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="C54" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D54" s="39"/>
+      <c r="D54" s="37"/>
       <c r="E54" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="F54" s="1"/>
+        <v>131</v>
+      </c>
+      <c r="F54" s="23"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="26"/>
-      <c r="B55" s="38" t="s">
-        <v>112</v>
-      </c>
-      <c r="C55" s="24" t="s">
+      <c r="A55" s="33" t="s">
+        <v>132</v>
+      </c>
+      <c r="B55" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="C55" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D55" s="39"/>
-      <c r="E55" s="43" t="s">
-        <v>113</v>
-      </c>
-      <c r="F55" s="1"/>
+      <c r="D55" s="37"/>
+      <c r="E55" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="F55" s="23"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="26"/>
-      <c r="B56" s="38" t="s">
-        <v>114</v>
-      </c>
-      <c r="C56" s="24" t="s">
+      <c r="A56" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="B56" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="C56" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D56" s="39"/>
-      <c r="E56" s="43" t="s">
-        <v>115</v>
-      </c>
-      <c r="F56" s="1"/>
+      <c r="D56" s="37"/>
+      <c r="E56" s="40" t="s">
+        <v>137</v>
+      </c>
+      <c r="F56" s="23"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="26"/>
-      <c r="B57" s="38" t="s">
-        <v>116</v>
-      </c>
-      <c r="C57" s="24" t="s">
+      <c r="A57" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="B57" s="36" t="s">
+        <v>139</v>
+      </c>
+      <c r="C57" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D57" s="39"/>
-      <c r="E57" s="44" t="s">
-        <v>117</v>
-      </c>
-      <c r="F57" s="1"/>
+      <c r="D57" s="37"/>
+      <c r="E57" s="41" t="s">
+        <v>140</v>
+      </c>
+      <c r="F57" s="23"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="45"/>
-      <c r="B58" s="46" t="s">
-        <v>118</v>
-      </c>
-      <c r="C58" s="24" t="s">
+      <c r="A58" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="B58" s="42" t="s">
+        <v>142</v>
+      </c>
+      <c r="C58" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D58" s="47"/>
-      <c r="E58" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="F58" s="1"/>
+      <c r="D58" s="43"/>
+      <c r="E58" s="40" t="s">
+        <v>143</v>
+      </c>
+      <c r="F58" s="27"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="48"/>
-      <c r="B59" s="49"/>
-      <c r="C59" s="50"/>
-      <c r="D59" s="50"/>
-      <c r="E59" s="51"/>
+      <c r="A59" s="44"/>
+      <c r="B59" s="45"/>
+      <c r="C59" s="46"/>
+      <c r="D59" s="46"/>
+      <c r="E59" s="47"/>
       <c r="F59" s="1"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
@@ -2798,7 +2954,7 @@
       <c r="B60" s="1"/>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
-      <c r="E60" s="52"/>
+      <c r="E60" s="48"/>
       <c r="F60" s="1"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
@@ -2806,7 +2962,7 @@
       <c r="B61" s="1"/>
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
-      <c r="E61" s="52"/>
+      <c r="E61" s="48"/>
       <c r="F61" s="1"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
@@ -2814,7 +2970,7 @@
       <c r="B62" s="1"/>
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
-      <c r="E62" s="52"/>
+      <c r="E62" s="48"/>
       <c r="F62" s="1"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
@@ -2822,7 +2978,7 @@
         <v>0</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
@@ -2863,7 +3019,7 @@
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="6" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="B67" s="7"/>
       <c r="C67" s="8" t="s">
@@ -2875,7 +3031,7 @@
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="11" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="B68" s="7"/>
       <c r="C68" s="12"/>
@@ -2897,238 +3053,268 @@
       <c r="E69" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="F69" s="53" t="s">
+      <c r="F69" s="49" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="17"/>
-      <c r="B70" s="54" t="s">
-        <v>123</v>
-      </c>
-      <c r="C70" s="24" t="s">
+      <c r="A70" s="33" t="s">
+        <v>147</v>
+      </c>
+      <c r="B70" s="50" t="s">
+        <v>148</v>
+      </c>
+      <c r="C70" s="25" t="s">
         <v>18</v>
       </c>
       <c r="D70" s="20"/>
-      <c r="E70" s="54" t="s">
-        <v>124</v>
-      </c>
-      <c r="F70" s="36">
-        <v>0.7</v>
+      <c r="E70" s="50" t="s">
+        <v>149</v>
+      </c>
+      <c r="F70" s="22">
+        <v>1.0</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="37"/>
-      <c r="B71" s="55" t="s">
-        <v>125</v>
-      </c>
-      <c r="C71" s="24" t="s">
+      <c r="A71" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="B71" s="51" t="s">
+        <v>151</v>
+      </c>
+      <c r="C71" s="25" t="s">
         <v>18</v>
       </c>
       <c r="D71" s="20"/>
-      <c r="E71" s="54" t="s">
-        <v>126</v>
-      </c>
-      <c r="F71" s="22"/>
+      <c r="E71" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="F71" s="23"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="37"/>
-      <c r="B72" s="55" t="s">
-        <v>127</v>
-      </c>
-      <c r="C72" s="24" t="s">
+      <c r="A72" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="B72" s="51" t="s">
+        <v>154</v>
+      </c>
+      <c r="C72" s="25" t="s">
         <v>18</v>
       </c>
       <c r="D72" s="20"/>
-      <c r="E72" s="54" t="s">
-        <v>128</v>
-      </c>
-      <c r="F72" s="22"/>
+      <c r="E72" s="50" t="s">
+        <v>155</v>
+      </c>
+      <c r="F72" s="23"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="37"/>
-      <c r="B73" s="54" t="s">
-        <v>129</v>
-      </c>
-      <c r="C73" s="24" t="s">
+      <c r="A73" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="B73" s="50" t="s">
+        <v>157</v>
+      </c>
+      <c r="C73" s="25" t="s">
         <v>18</v>
       </c>
       <c r="D73" s="20"/>
-      <c r="E73" s="54" t="s">
-        <v>130</v>
-      </c>
-      <c r="F73" s="22"/>
+      <c r="E73" s="50" t="s">
+        <v>158</v>
+      </c>
+      <c r="F73" s="23"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="37"/>
-      <c r="B74" s="55" t="s">
-        <v>131</v>
-      </c>
-      <c r="C74" s="24" t="s">
+      <c r="A74" s="33" t="s">
+        <v>159</v>
+      </c>
+      <c r="B74" s="51" t="s">
+        <v>160</v>
+      </c>
+      <c r="C74" s="25" t="s">
         <v>18</v>
       </c>
       <c r="D74" s="20"/>
-      <c r="E74" s="54" t="s">
-        <v>132</v>
-      </c>
-      <c r="F74" s="22"/>
+      <c r="E74" s="50" t="s">
+        <v>161</v>
+      </c>
+      <c r="F74" s="23"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="37"/>
-      <c r="B75" s="55" t="s">
-        <v>76</v>
-      </c>
-      <c r="C75" s="24" t="s">
+      <c r="A75" s="33" t="s">
+        <v>162</v>
+      </c>
+      <c r="B75" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="C75" s="25" t="s">
         <v>18</v>
       </c>
       <c r="D75" s="20"/>
-      <c r="E75" s="54" t="s">
-        <v>133</v>
-      </c>
-      <c r="F75" s="22"/>
+      <c r="E75" s="50" t="s">
+        <v>163</v>
+      </c>
+      <c r="F75" s="23"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="37"/>
-      <c r="B76" s="55" t="s">
-        <v>134</v>
-      </c>
-      <c r="C76" s="24" t="s">
+      <c r="A76" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="B76" s="51" t="s">
+        <v>165</v>
+      </c>
+      <c r="C76" s="25" t="s">
         <v>18</v>
       </c>
       <c r="D76" s="20"/>
-      <c r="E76" s="54" t="s">
-        <v>135</v>
-      </c>
-      <c r="F76" s="22"/>
+      <c r="E76" s="50" t="s">
+        <v>166</v>
+      </c>
+      <c r="F76" s="23"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="37"/>
-      <c r="B77" s="54" t="s">
-        <v>136</v>
-      </c>
-      <c r="C77" s="24" t="s">
+      <c r="A77" s="33" t="s">
+        <v>167</v>
+      </c>
+      <c r="B77" s="50" t="s">
+        <v>168</v>
+      </c>
+      <c r="C77" s="25" t="s">
         <v>18</v>
       </c>
       <c r="D77" s="20"/>
-      <c r="E77" s="54" t="s">
-        <v>137</v>
-      </c>
-      <c r="F77" s="22"/>
+      <c r="E77" s="50" t="s">
+        <v>169</v>
+      </c>
+      <c r="F77" s="23"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="37"/>
-      <c r="B78" s="54" t="s">
-        <v>138</v>
-      </c>
-      <c r="C78" s="24" t="s">
+      <c r="A78" s="33" t="s">
+        <v>170</v>
+      </c>
+      <c r="B78" s="50" t="s">
+        <v>171</v>
+      </c>
+      <c r="C78" s="25" t="s">
         <v>18</v>
       </c>
       <c r="D78" s="20"/>
-      <c r="E78" s="54" t="s">
-        <v>139</v>
-      </c>
-      <c r="F78" s="22"/>
+      <c r="E78" s="50" t="s">
+        <v>172</v>
+      </c>
+      <c r="F78" s="23"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="37"/>
-      <c r="B79" s="54" t="s">
-        <v>88</v>
-      </c>
-      <c r="C79" s="24" t="s">
+      <c r="A79" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="B79" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="C79" s="25" t="s">
         <v>18</v>
       </c>
       <c r="D79" s="20"/>
-      <c r="E79" s="56" t="s">
-        <v>140</v>
-      </c>
-      <c r="F79" s="22"/>
+      <c r="E79" s="52" t="s">
+        <v>174</v>
+      </c>
+      <c r="F79" s="23"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="37"/>
-      <c r="B80" s="55" t="s">
-        <v>141</v>
-      </c>
-      <c r="C80" s="24" t="s">
+      <c r="A80" s="33" t="s">
+        <v>175</v>
+      </c>
+      <c r="B80" s="51" t="s">
+        <v>176</v>
+      </c>
+      <c r="C80" s="25" t="s">
         <v>18</v>
       </c>
       <c r="D80" s="20"/>
-      <c r="E80" s="56" t="s">
-        <v>142</v>
-      </c>
-      <c r="F80" s="22"/>
+      <c r="E80" s="52" t="s">
+        <v>177</v>
+      </c>
+      <c r="F80" s="23"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="37"/>
-      <c r="B81" s="54" t="s">
-        <v>143</v>
-      </c>
-      <c r="C81" s="24" t="s">
+      <c r="A81" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B81" s="50" t="s">
+        <v>179</v>
+      </c>
+      <c r="C81" s="25" t="s">
         <v>18</v>
       </c>
       <c r="D81" s="20"/>
-      <c r="E81" s="54" t="s">
-        <v>144</v>
-      </c>
-      <c r="F81" s="22"/>
+      <c r="E81" s="50" t="s">
+        <v>180</v>
+      </c>
+      <c r="F81" s="23"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="37"/>
-      <c r="B82" s="54" t="s">
-        <v>145</v>
-      </c>
-      <c r="C82" s="24" t="s">
+      <c r="A82" s="33" t="s">
+        <v>181</v>
+      </c>
+      <c r="B82" s="50" t="s">
+        <v>182</v>
+      </c>
+      <c r="C82" s="25" t="s">
         <v>18</v>
       </c>
       <c r="D82" s="20"/>
-      <c r="E82" s="54" t="s">
-        <v>146</v>
-      </c>
-      <c r="F82" s="28"/>
+      <c r="E82" s="50" t="s">
+        <v>183</v>
+      </c>
+      <c r="F82" s="23"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="57"/>
-      <c r="B83" s="58" t="s">
-        <v>147</v>
-      </c>
-      <c r="C83" s="24" t="s">
+      <c r="A83" s="33" t="s">
+        <v>184</v>
+      </c>
+      <c r="B83" s="52" t="s">
+        <v>185</v>
+      </c>
+      <c r="C83" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D83" s="59"/>
-      <c r="E83" s="56" t="s">
-        <v>148</v>
-      </c>
-      <c r="F83" s="40"/>
+      <c r="D83" s="53"/>
+      <c r="E83" s="52" t="s">
+        <v>186</v>
+      </c>
+      <c r="F83" s="23"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="57"/>
-      <c r="B84" s="58" t="s">
-        <v>149</v>
-      </c>
-      <c r="C84" s="24" t="s">
+      <c r="A84" s="33" t="s">
+        <v>187</v>
+      </c>
+      <c r="B84" s="52" t="s">
+        <v>188</v>
+      </c>
+      <c r="C84" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D84" s="59"/>
-      <c r="E84" s="54" t="s">
-        <v>150</v>
-      </c>
-      <c r="F84" s="40"/>
+      <c r="D84" s="53"/>
+      <c r="E84" s="50" t="s">
+        <v>189</v>
+      </c>
+      <c r="F84" s="27"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="C85" s="2"/>
       <c r="D85" s="2"/>
-      <c r="E85" s="60"/>
-      <c r="F85" s="40"/>
+      <c r="E85" s="54"/>
+      <c r="F85" s="55"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="C86" s="2"/>
       <c r="D86" s="2"/>
-      <c r="E86" s="60"/>
+      <c r="E86" s="54"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="C87" s="2"/>
       <c r="D87" s="2"/>
-      <c r="E87" s="53" t="s">
-        <v>151</v>
+      <c r="E87" s="49" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="88" ht="15.75" customHeight="1">
@@ -6883,12 +7069,12 @@
   <mergeCells count="15">
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="C33:F33"/>
-    <mergeCell ref="F35:F45"/>
     <mergeCell ref="A67:B67"/>
     <mergeCell ref="C67:F67"/>
     <mergeCell ref="A68:B68"/>
     <mergeCell ref="C68:F68"/>
-    <mergeCell ref="F70:F82"/>
+    <mergeCell ref="F35:F58"/>
+    <mergeCell ref="F70:F84"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="A6:B6"/>
@@ -6922,758 +7108,758 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="61" t="s">
-        <v>152</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="61" t="s">
-        <v>153</v>
-      </c>
-      <c r="D1" s="62"/>
-      <c r="E1" s="63" t="s">
-        <v>154</v>
-      </c>
-      <c r="F1" s="63" t="s">
-        <v>155</v>
-      </c>
-      <c r="G1" s="64"/>
+      <c r="A1" s="56" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="57"/>
+      <c r="C1" s="56" t="s">
+        <v>192</v>
+      </c>
+      <c r="D1" s="57"/>
+      <c r="E1" s="58" t="s">
+        <v>193</v>
+      </c>
+      <c r="F1" s="58" t="s">
+        <v>194</v>
+      </c>
+      <c r="G1" s="59"/>
     </row>
     <row r="2">
-      <c r="A2" s="65" t="s">
-        <v>156</v>
-      </c>
-      <c r="B2" s="65" t="s">
+      <c r="A2" s="60" t="s">
+        <v>195</v>
+      </c>
+      <c r="B2" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="65" t="s">
-        <v>157</v>
-      </c>
-      <c r="D2" s="65" t="s">
-        <v>158</v>
-      </c>
-      <c r="E2" s="65" t="s">
-        <v>159</v>
-      </c>
-      <c r="F2" s="65" t="s">
-        <v>160</v>
-      </c>
-      <c r="G2" s="65" t="s">
-        <v>161</v>
+      <c r="C2" s="60" t="s">
+        <v>196</v>
+      </c>
+      <c r="D2" s="60" t="s">
+        <v>197</v>
+      </c>
+      <c r="E2" s="60" t="s">
+        <v>198</v>
+      </c>
+      <c r="F2" s="60" t="s">
+        <v>199</v>
+      </c>
+      <c r="G2" s="60" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="66" t="s">
-        <v>162</v>
-      </c>
-      <c r="D3" s="67" t="s">
-        <v>163</v>
-      </c>
-      <c r="E3" s="66" t="s">
-        <v>164</v>
-      </c>
-      <c r="F3" s="66" t="s">
-        <v>165</v>
-      </c>
-      <c r="G3" s="66" t="s">
-        <v>166</v>
-      </c>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="68"/>
-      <c r="O3" s="68"/>
-      <c r="P3" s="68"/>
-      <c r="Q3" s="68"/>
-      <c r="R3" s="68"/>
-      <c r="S3" s="68"/>
-      <c r="T3" s="68"/>
-      <c r="U3" s="68"/>
-      <c r="V3" s="68"/>
-      <c r="W3" s="68"/>
-      <c r="X3" s="68"/>
-      <c r="Y3" s="68"/>
-      <c r="Z3" s="68"/>
+      <c r="C3" s="62" t="s">
+        <v>201</v>
+      </c>
+      <c r="D3" s="63" t="s">
+        <v>202</v>
+      </c>
+      <c r="E3" s="62" t="s">
+        <v>203</v>
+      </c>
+      <c r="F3" s="62" t="s">
+        <v>204</v>
+      </c>
+      <c r="G3" s="62" t="s">
+        <v>205</v>
+      </c>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="64"/>
+      <c r="L3" s="64"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="64"/>
+      <c r="V3" s="64"/>
+      <c r="W3" s="64"/>
+      <c r="X3" s="64"/>
+      <c r="Y3" s="64"/>
+      <c r="Z3" s="64"/>
     </row>
     <row r="4">
       <c r="A4" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="66" t="s">
-        <v>167</v>
-      </c>
-      <c r="D4" s="67" t="s">
-        <v>168</v>
-      </c>
-      <c r="E4" s="69" t="s">
-        <v>169</v>
-      </c>
-      <c r="F4" s="69" t="s">
-        <v>169</v>
-      </c>
-      <c r="G4" s="66" t="s">
-        <v>166</v>
-      </c>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68"/>
-      <c r="L4" s="68"/>
-      <c r="M4" s="68"/>
-      <c r="N4" s="68"/>
-      <c r="O4" s="68"/>
-      <c r="P4" s="68"/>
-      <c r="Q4" s="68"/>
-      <c r="R4" s="68"/>
-      <c r="S4" s="68"/>
-      <c r="T4" s="68"/>
-      <c r="U4" s="68"/>
-      <c r="V4" s="68"/>
-      <c r="W4" s="68"/>
-      <c r="X4" s="68"/>
-      <c r="Y4" s="68"/>
-      <c r="Z4" s="68"/>
+      <c r="C4" s="62" t="s">
+        <v>206</v>
+      </c>
+      <c r="D4" s="63" t="s">
+        <v>207</v>
+      </c>
+      <c r="E4" s="65" t="s">
+        <v>208</v>
+      </c>
+      <c r="F4" s="65" t="s">
+        <v>208</v>
+      </c>
+      <c r="G4" s="62" t="s">
+        <v>205</v>
+      </c>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
+      <c r="K4" s="64"/>
+      <c r="L4" s="64"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="64"/>
+      <c r="W4" s="64"/>
+      <c r="X4" s="64"/>
+      <c r="Y4" s="64"/>
+      <c r="Z4" s="64"/>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="66" t="s">
+      <c r="B5" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="66" t="s">
-        <v>170</v>
-      </c>
-      <c r="D5" s="67" t="s">
-        <v>171</v>
-      </c>
-      <c r="E5" s="69" t="s">
-        <v>172</v>
-      </c>
-      <c r="F5" s="70" t="s">
-        <v>173</v>
-      </c>
-      <c r="G5" s="71" t="s">
-        <v>174</v>
-      </c>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="68"/>
-      <c r="L5" s="68"/>
-      <c r="M5" s="68"/>
-      <c r="N5" s="68"/>
-      <c r="O5" s="68"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="68"/>
-      <c r="T5" s="68"/>
-      <c r="U5" s="68"/>
-      <c r="V5" s="68"/>
-      <c r="W5" s="68"/>
-      <c r="X5" s="68"/>
-      <c r="Y5" s="68"/>
-      <c r="Z5" s="68"/>
+      <c r="C5" s="62" t="s">
+        <v>209</v>
+      </c>
+      <c r="D5" s="63" t="s">
+        <v>210</v>
+      </c>
+      <c r="E5" s="65" t="s">
+        <v>211</v>
+      </c>
+      <c r="F5" s="66" t="s">
+        <v>212</v>
+      </c>
+      <c r="G5" s="67" t="s">
+        <v>213</v>
+      </c>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="64"/>
+      <c r="K5" s="64"/>
+      <c r="L5" s="64"/>
+      <c r="M5" s="64"/>
+      <c r="N5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="64"/>
+      <c r="Q5" s="64"/>
+      <c r="R5" s="64"/>
+      <c r="S5" s="64"/>
+      <c r="T5" s="64"/>
+      <c r="U5" s="64"/>
+      <c r="V5" s="64"/>
+      <c r="W5" s="64"/>
+      <c r="X5" s="64"/>
+      <c r="Y5" s="64"/>
+      <c r="Z5" s="64"/>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="66" t="s">
-        <v>175</v>
-      </c>
-      <c r="D6" s="67" t="s">
-        <v>176</v>
-      </c>
-      <c r="E6" s="69" t="s">
-        <v>177</v>
-      </c>
-      <c r="F6" s="69" t="s">
-        <v>177</v>
-      </c>
-      <c r="G6" s="66" t="s">
-        <v>166</v>
-      </c>
-      <c r="H6" s="68"/>
-      <c r="I6" s="68"/>
-      <c r="J6" s="68"/>
-      <c r="K6" s="68"/>
-      <c r="L6" s="68"/>
-      <c r="M6" s="68"/>
-      <c r="N6" s="68"/>
-      <c r="O6" s="68"/>
-      <c r="P6" s="68"/>
-      <c r="Q6" s="68"/>
-      <c r="R6" s="68"/>
-      <c r="S6" s="68"/>
-      <c r="T6" s="68"/>
-      <c r="U6" s="68"/>
-      <c r="V6" s="68"/>
-      <c r="W6" s="68"/>
-      <c r="X6" s="68"/>
-      <c r="Y6" s="68"/>
-      <c r="Z6" s="68"/>
+      <c r="C6" s="62" t="s">
+        <v>214</v>
+      </c>
+      <c r="D6" s="63" t="s">
+        <v>215</v>
+      </c>
+      <c r="E6" s="65" t="s">
+        <v>216</v>
+      </c>
+      <c r="F6" s="65" t="s">
+        <v>216</v>
+      </c>
+      <c r="G6" s="62" t="s">
+        <v>205</v>
+      </c>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="64"/>
+      <c r="L6" s="64"/>
+      <c r="M6" s="64"/>
+      <c r="N6" s="64"/>
+      <c r="O6" s="64"/>
+      <c r="P6" s="64"/>
+      <c r="Q6" s="64"/>
+      <c r="R6" s="64"/>
+      <c r="S6" s="64"/>
+      <c r="T6" s="64"/>
+      <c r="U6" s="64"/>
+      <c r="V6" s="64"/>
+      <c r="W6" s="64"/>
+      <c r="X6" s="64"/>
+      <c r="Y6" s="64"/>
+      <c r="Z6" s="64"/>
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="61" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="66" t="s">
-        <v>178</v>
-      </c>
-      <c r="D7" s="67" t="s">
-        <v>179</v>
-      </c>
-      <c r="E7" s="69" t="s">
-        <v>180</v>
-      </c>
-      <c r="F7" s="69" t="s">
-        <v>180</v>
-      </c>
-      <c r="G7" s="66" t="s">
-        <v>166</v>
-      </c>
-      <c r="H7" s="68"/>
-      <c r="I7" s="68"/>
-      <c r="J7" s="68"/>
-      <c r="K7" s="68"/>
-      <c r="L7" s="68"/>
-      <c r="M7" s="68"/>
-      <c r="N7" s="68"/>
-      <c r="O7" s="68"/>
-      <c r="P7" s="68"/>
-      <c r="Q7" s="68"/>
-      <c r="R7" s="68"/>
-      <c r="S7" s="68"/>
-      <c r="T7" s="68"/>
-      <c r="U7" s="68"/>
-      <c r="V7" s="68"/>
-      <c r="W7" s="68"/>
-      <c r="X7" s="68"/>
-      <c r="Y7" s="68"/>
-      <c r="Z7" s="68"/>
+      <c r="C7" s="62" t="s">
+        <v>217</v>
+      </c>
+      <c r="D7" s="63" t="s">
+        <v>218</v>
+      </c>
+      <c r="E7" s="65" t="s">
+        <v>219</v>
+      </c>
+      <c r="F7" s="65" t="s">
+        <v>219</v>
+      </c>
+      <c r="G7" s="62" t="s">
+        <v>205</v>
+      </c>
+      <c r="H7" s="64"/>
+      <c r="I7" s="64"/>
+      <c r="J7" s="64"/>
+      <c r="K7" s="64"/>
+      <c r="L7" s="64"/>
+      <c r="M7" s="64"/>
+      <c r="N7" s="64"/>
+      <c r="O7" s="64"/>
+      <c r="P7" s="64"/>
+      <c r="Q7" s="64"/>
+      <c r="R7" s="64"/>
+      <c r="S7" s="64"/>
+      <c r="T7" s="64"/>
+      <c r="U7" s="64"/>
+      <c r="V7" s="64"/>
+      <c r="W7" s="64"/>
+      <c r="X7" s="64"/>
+      <c r="Y7" s="64"/>
+      <c r="Z7" s="64"/>
     </row>
     <row r="8">
       <c r="A8" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="37" t="s">
+      <c r="B8" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="66" t="s">
-        <v>181</v>
-      </c>
-      <c r="D8" s="67" t="s">
-        <v>182</v>
-      </c>
-      <c r="E8" s="69" t="s">
-        <v>183</v>
-      </c>
-      <c r="F8" s="69" t="s">
-        <v>184</v>
-      </c>
-      <c r="G8" s="66" t="s">
-        <v>166</v>
-      </c>
-      <c r="H8" s="68"/>
-      <c r="I8" s="68"/>
-      <c r="J8" s="68"/>
-      <c r="K8" s="68"/>
-      <c r="L8" s="68"/>
-      <c r="M8" s="68"/>
-      <c r="N8" s="68"/>
-      <c r="O8" s="68"/>
-      <c r="P8" s="68"/>
-      <c r="Q8" s="68"/>
-      <c r="R8" s="68"/>
-      <c r="S8" s="68"/>
-      <c r="T8" s="68"/>
-      <c r="U8" s="68"/>
-      <c r="V8" s="68"/>
-      <c r="W8" s="68"/>
-      <c r="X8" s="68"/>
-      <c r="Y8" s="68"/>
-      <c r="Z8" s="68"/>
+      <c r="C8" s="62" t="s">
+        <v>220</v>
+      </c>
+      <c r="D8" s="63" t="s">
+        <v>221</v>
+      </c>
+      <c r="E8" s="65" t="s">
+        <v>222</v>
+      </c>
+      <c r="F8" s="65" t="s">
+        <v>223</v>
+      </c>
+      <c r="G8" s="62" t="s">
+        <v>205</v>
+      </c>
+      <c r="H8" s="64"/>
+      <c r="I8" s="64"/>
+      <c r="J8" s="64"/>
+      <c r="K8" s="64"/>
+      <c r="L8" s="64"/>
+      <c r="M8" s="64"/>
+      <c r="N8" s="64"/>
+      <c r="O8" s="64"/>
+      <c r="P8" s="64"/>
+      <c r="Q8" s="64"/>
+      <c r="R8" s="64"/>
+      <c r="S8" s="64"/>
+      <c r="T8" s="64"/>
+      <c r="U8" s="64"/>
+      <c r="V8" s="64"/>
+      <c r="W8" s="64"/>
+      <c r="X8" s="64"/>
+      <c r="Y8" s="64"/>
+      <c r="Z8" s="64"/>
     </row>
     <row r="9">
       <c r="A9" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="37" t="s">
+      <c r="B9" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="66" t="s">
-        <v>185</v>
-      </c>
-      <c r="D9" s="67" t="s">
-        <v>186</v>
-      </c>
-      <c r="E9" s="69" t="s">
-        <v>187</v>
-      </c>
-      <c r="F9" s="69" t="s">
-        <v>188</v>
-      </c>
-      <c r="G9" s="66" t="s">
-        <v>166</v>
-      </c>
-      <c r="H9" s="68"/>
-      <c r="I9" s="68"/>
-      <c r="J9" s="68"/>
-      <c r="K9" s="68"/>
-      <c r="L9" s="68"/>
-      <c r="M9" s="68"/>
-      <c r="N9" s="68"/>
-      <c r="O9" s="68"/>
-      <c r="P9" s="68"/>
-      <c r="Q9" s="68"/>
-      <c r="R9" s="68"/>
-      <c r="S9" s="68"/>
-      <c r="T9" s="68"/>
-      <c r="U9" s="68"/>
-      <c r="V9" s="68"/>
-      <c r="W9" s="68"/>
-      <c r="X9" s="68"/>
-      <c r="Y9" s="68"/>
-      <c r="Z9" s="68"/>
+      <c r="C9" s="62" t="s">
+        <v>224</v>
+      </c>
+      <c r="D9" s="63" t="s">
+        <v>225</v>
+      </c>
+      <c r="E9" s="65" t="s">
+        <v>226</v>
+      </c>
+      <c r="F9" s="65" t="s">
+        <v>227</v>
+      </c>
+      <c r="G9" s="62" t="s">
+        <v>205</v>
+      </c>
+      <c r="H9" s="64"/>
+      <c r="I9" s="64"/>
+      <c r="J9" s="64"/>
+      <c r="K9" s="64"/>
+      <c r="L9" s="64"/>
+      <c r="M9" s="64"/>
+      <c r="N9" s="64"/>
+      <c r="O9" s="64"/>
+      <c r="P9" s="64"/>
+      <c r="Q9" s="64"/>
+      <c r="R9" s="64"/>
+      <c r="S9" s="64"/>
+      <c r="T9" s="64"/>
+      <c r="U9" s="64"/>
+      <c r="V9" s="64"/>
+      <c r="W9" s="64"/>
+      <c r="X9" s="64"/>
+      <c r="Y9" s="64"/>
+      <c r="Z9" s="64"/>
     </row>
     <row r="10">
       <c r="A10" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="37" t="s">
+      <c r="B10" s="61" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="66" t="s">
-        <v>189</v>
-      </c>
-      <c r="D10" s="67" t="s">
-        <v>186</v>
-      </c>
-      <c r="E10" s="69" t="s">
-        <v>190</v>
-      </c>
-      <c r="F10" s="69" t="s">
-        <v>190</v>
-      </c>
-      <c r="G10" s="66" t="s">
-        <v>166</v>
-      </c>
-      <c r="H10" s="68"/>
-      <c r="I10" s="68"/>
-      <c r="J10" s="68"/>
-      <c r="K10" s="68"/>
-      <c r="L10" s="68"/>
-      <c r="M10" s="68"/>
-      <c r="N10" s="68"/>
-      <c r="O10" s="68"/>
-      <c r="P10" s="68"/>
-      <c r="Q10" s="68"/>
-      <c r="R10" s="68"/>
-      <c r="S10" s="68"/>
-      <c r="T10" s="68"/>
-      <c r="U10" s="68"/>
-      <c r="V10" s="68"/>
-      <c r="W10" s="68"/>
-      <c r="X10" s="68"/>
-      <c r="Y10" s="68"/>
-      <c r="Z10" s="68"/>
+      <c r="C10" s="62" t="s">
+        <v>228</v>
+      </c>
+      <c r="D10" s="63" t="s">
+        <v>225</v>
+      </c>
+      <c r="E10" s="65" t="s">
+        <v>229</v>
+      </c>
+      <c r="F10" s="65" t="s">
+        <v>229</v>
+      </c>
+      <c r="G10" s="62" t="s">
+        <v>205</v>
+      </c>
+      <c r="H10" s="64"/>
+      <c r="I10" s="64"/>
+      <c r="J10" s="64"/>
+      <c r="K10" s="64"/>
+      <c r="L10" s="64"/>
+      <c r="M10" s="64"/>
+      <c r="N10" s="64"/>
+      <c r="O10" s="64"/>
+      <c r="P10" s="64"/>
+      <c r="Q10" s="64"/>
+      <c r="R10" s="64"/>
+      <c r="S10" s="64"/>
+      <c r="T10" s="64"/>
+      <c r="U10" s="64"/>
+      <c r="V10" s="64"/>
+      <c r="W10" s="64"/>
+      <c r="X10" s="64"/>
+      <c r="Y10" s="64"/>
+      <c r="Z10" s="64"/>
     </row>
     <row r="11">
       <c r="A11" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="37" t="s">
+      <c r="B11" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="66" t="s">
-        <v>191</v>
-      </c>
-      <c r="D11" s="67" t="s">
-        <v>192</v>
-      </c>
-      <c r="E11" s="69" t="s">
-        <v>193</v>
-      </c>
-      <c r="F11" s="69" t="s">
-        <v>194</v>
-      </c>
-      <c r="G11" s="66" t="s">
-        <v>166</v>
-      </c>
-      <c r="H11" s="68"/>
-      <c r="I11" s="68"/>
-      <c r="J11" s="68"/>
-      <c r="K11" s="68"/>
-      <c r="L11" s="68"/>
-      <c r="M11" s="68"/>
-      <c r="N11" s="68"/>
-      <c r="O11" s="68"/>
-      <c r="P11" s="68"/>
-      <c r="Q11" s="68"/>
-      <c r="R11" s="68"/>
-      <c r="S11" s="68"/>
-      <c r="T11" s="68"/>
-      <c r="U11" s="68"/>
-      <c r="V11" s="68"/>
-      <c r="W11" s="68"/>
-      <c r="X11" s="68"/>
-      <c r="Y11" s="68"/>
-      <c r="Z11" s="68"/>
+      <c r="C11" s="62" t="s">
+        <v>230</v>
+      </c>
+      <c r="D11" s="63" t="s">
+        <v>231</v>
+      </c>
+      <c r="E11" s="65" t="s">
+        <v>232</v>
+      </c>
+      <c r="F11" s="65" t="s">
+        <v>233</v>
+      </c>
+      <c r="G11" s="62" t="s">
+        <v>205</v>
+      </c>
+      <c r="H11" s="64"/>
+      <c r="I11" s="64"/>
+      <c r="J11" s="64"/>
+      <c r="K11" s="64"/>
+      <c r="L11" s="64"/>
+      <c r="M11" s="64"/>
+      <c r="N11" s="64"/>
+      <c r="O11" s="64"/>
+      <c r="P11" s="64"/>
+      <c r="Q11" s="64"/>
+      <c r="R11" s="64"/>
+      <c r="S11" s="64"/>
+      <c r="T11" s="64"/>
+      <c r="U11" s="64"/>
+      <c r="V11" s="64"/>
+      <c r="W11" s="64"/>
+      <c r="X11" s="64"/>
+      <c r="Y11" s="64"/>
+      <c r="Z11" s="64"/>
     </row>
     <row r="12">
       <c r="A12" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="37" t="s">
+      <c r="B12" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="66" t="s">
-        <v>195</v>
-      </c>
-      <c r="D12" s="67" t="s">
-        <v>196</v>
-      </c>
-      <c r="E12" s="69" t="s">
-        <v>197</v>
-      </c>
-      <c r="F12" s="69" t="s">
-        <v>197</v>
-      </c>
-      <c r="G12" s="66" t="s">
-        <v>166</v>
-      </c>
-      <c r="H12" s="68"/>
-      <c r="I12" s="68"/>
-      <c r="J12" s="68"/>
-      <c r="K12" s="68"/>
-      <c r="L12" s="68"/>
-      <c r="M12" s="68"/>
-      <c r="N12" s="68"/>
-      <c r="O12" s="68"/>
-      <c r="P12" s="68"/>
-      <c r="Q12" s="68"/>
-      <c r="R12" s="68"/>
-      <c r="S12" s="68"/>
-      <c r="T12" s="68"/>
-      <c r="U12" s="68"/>
-      <c r="V12" s="68"/>
-      <c r="W12" s="68"/>
-      <c r="X12" s="68"/>
-      <c r="Y12" s="68"/>
-      <c r="Z12" s="68"/>
+      <c r="C12" s="62" t="s">
+        <v>234</v>
+      </c>
+      <c r="D12" s="63" t="s">
+        <v>235</v>
+      </c>
+      <c r="E12" s="65" t="s">
+        <v>236</v>
+      </c>
+      <c r="F12" s="65" t="s">
+        <v>236</v>
+      </c>
+      <c r="G12" s="62" t="s">
+        <v>205</v>
+      </c>
+      <c r="H12" s="64"/>
+      <c r="I12" s="64"/>
+      <c r="J12" s="64"/>
+      <c r="K12" s="64"/>
+      <c r="L12" s="64"/>
+      <c r="M12" s="64"/>
+      <c r="N12" s="64"/>
+      <c r="O12" s="64"/>
+      <c r="P12" s="64"/>
+      <c r="Q12" s="64"/>
+      <c r="R12" s="64"/>
+      <c r="S12" s="64"/>
+      <c r="T12" s="64"/>
+      <c r="U12" s="64"/>
+      <c r="V12" s="64"/>
+      <c r="W12" s="64"/>
+      <c r="X12" s="64"/>
+      <c r="Y12" s="64"/>
+      <c r="Z12" s="64"/>
     </row>
     <row r="13">
       <c r="A13" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="66" t="s">
+      <c r="B13" s="62" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="66" t="s">
-        <v>198</v>
-      </c>
-      <c r="D13" s="66" t="s">
-        <v>199</v>
-      </c>
-      <c r="E13" s="66" t="s">
-        <v>200</v>
-      </c>
-      <c r="F13" s="66" t="s">
-        <v>201</v>
-      </c>
-      <c r="G13" s="66" t="s">
-        <v>166</v>
-      </c>
-      <c r="H13" s="68"/>
-      <c r="I13" s="68"/>
-      <c r="J13" s="68"/>
-      <c r="K13" s="68"/>
-      <c r="L13" s="68"/>
-      <c r="M13" s="68"/>
-      <c r="N13" s="68"/>
-      <c r="O13" s="68"/>
-      <c r="P13" s="68"/>
-      <c r="Q13" s="68"/>
-      <c r="R13" s="68"/>
-      <c r="S13" s="68"/>
-      <c r="T13" s="68"/>
-      <c r="U13" s="68"/>
-      <c r="V13" s="68"/>
-      <c r="W13" s="68"/>
-      <c r="X13" s="68"/>
-      <c r="Y13" s="68"/>
-      <c r="Z13" s="68"/>
+      <c r="C13" s="62" t="s">
+        <v>237</v>
+      </c>
+      <c r="D13" s="62" t="s">
+        <v>238</v>
+      </c>
+      <c r="E13" s="62" t="s">
+        <v>239</v>
+      </c>
+      <c r="F13" s="62" t="s">
+        <v>240</v>
+      </c>
+      <c r="G13" s="62" t="s">
+        <v>205</v>
+      </c>
+      <c r="H13" s="64"/>
+      <c r="I13" s="64"/>
+      <c r="J13" s="64"/>
+      <c r="K13" s="64"/>
+      <c r="L13" s="64"/>
+      <c r="M13" s="64"/>
+      <c r="N13" s="64"/>
+      <c r="O13" s="64"/>
+      <c r="P13" s="64"/>
+      <c r="Q13" s="64"/>
+      <c r="R13" s="64"/>
+      <c r="S13" s="64"/>
+      <c r="T13" s="64"/>
+      <c r="U13" s="64"/>
+      <c r="V13" s="64"/>
+      <c r="W13" s="64"/>
+      <c r="X13" s="64"/>
+      <c r="Y13" s="64"/>
+      <c r="Z13" s="64"/>
     </row>
     <row r="14">
       <c r="A14" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="66" t="s">
+      <c r="B14" s="62" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="66" t="s">
-        <v>202</v>
-      </c>
-      <c r="D14" s="66" t="s">
-        <v>203</v>
-      </c>
-      <c r="E14" s="66" t="s">
-        <v>204</v>
-      </c>
-      <c r="F14" s="66" t="s">
-        <v>204</v>
-      </c>
-      <c r="G14" s="66" t="s">
-        <v>166</v>
-      </c>
-      <c r="H14" s="68"/>
-      <c r="I14" s="68"/>
-      <c r="J14" s="68"/>
-      <c r="K14" s="68"/>
-      <c r="L14" s="68"/>
-      <c r="M14" s="68"/>
-      <c r="N14" s="68"/>
-      <c r="O14" s="68"/>
-      <c r="P14" s="68"/>
-      <c r="Q14" s="68"/>
-      <c r="R14" s="68"/>
-      <c r="S14" s="68"/>
-      <c r="T14" s="68"/>
-      <c r="U14" s="68"/>
-      <c r="V14" s="68"/>
-      <c r="W14" s="68"/>
-      <c r="X14" s="68"/>
-      <c r="Y14" s="68"/>
-      <c r="Z14" s="68"/>
+      <c r="C14" s="62" t="s">
+        <v>241</v>
+      </c>
+      <c r="D14" s="62" t="s">
+        <v>242</v>
+      </c>
+      <c r="E14" s="62" t="s">
+        <v>243</v>
+      </c>
+      <c r="F14" s="62" t="s">
+        <v>243</v>
+      </c>
+      <c r="G14" s="62" t="s">
+        <v>205</v>
+      </c>
+      <c r="H14" s="64"/>
+      <c r="I14" s="64"/>
+      <c r="J14" s="64"/>
+      <c r="K14" s="64"/>
+      <c r="L14" s="64"/>
+      <c r="M14" s="64"/>
+      <c r="N14" s="64"/>
+      <c r="O14" s="64"/>
+      <c r="P14" s="64"/>
+      <c r="Q14" s="64"/>
+      <c r="R14" s="64"/>
+      <c r="S14" s="64"/>
+      <c r="T14" s="64"/>
+      <c r="U14" s="64"/>
+      <c r="V14" s="64"/>
+      <c r="W14" s="64"/>
+      <c r="X14" s="64"/>
+      <c r="Y14" s="64"/>
+      <c r="Z14" s="64"/>
     </row>
     <row r="15">
       <c r="A15" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="B15" s="66" t="s">
+      <c r="B15" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="66" t="s">
+      <c r="C15" s="62" t="s">
+        <v>244</v>
+      </c>
+      <c r="D15" s="62" t="s">
+        <v>245</v>
+      </c>
+      <c r="E15" s="62" t="s">
+        <v>246</v>
+      </c>
+      <c r="F15" s="62" t="s">
+        <v>247</v>
+      </c>
+      <c r="G15" s="62" t="s">
         <v>205</v>
       </c>
-      <c r="D15" s="66" t="s">
-        <v>206</v>
-      </c>
-      <c r="E15" s="66" t="s">
-        <v>207</v>
-      </c>
-      <c r="F15" s="66" t="s">
-        <v>208</v>
-      </c>
-      <c r="G15" s="66" t="s">
-        <v>166</v>
-      </c>
-      <c r="H15" s="68"/>
-      <c r="I15" s="68"/>
-      <c r="J15" s="68"/>
-      <c r="K15" s="68"/>
-      <c r="L15" s="68"/>
-      <c r="M15" s="68"/>
-      <c r="N15" s="68"/>
-      <c r="O15" s="68"/>
-      <c r="P15" s="68"/>
-      <c r="Q15" s="68"/>
-      <c r="R15" s="68"/>
-      <c r="S15" s="68"/>
-      <c r="T15" s="68"/>
-      <c r="U15" s="68"/>
-      <c r="V15" s="68"/>
-      <c r="W15" s="68"/>
-      <c r="X15" s="68"/>
-      <c r="Y15" s="68"/>
-      <c r="Z15" s="68"/>
+      <c r="H15" s="64"/>
+      <c r="I15" s="64"/>
+      <c r="J15" s="64"/>
+      <c r="K15" s="64"/>
+      <c r="L15" s="64"/>
+      <c r="M15" s="64"/>
+      <c r="N15" s="64"/>
+      <c r="O15" s="64"/>
+      <c r="P15" s="64"/>
+      <c r="Q15" s="64"/>
+      <c r="R15" s="64"/>
+      <c r="S15" s="64"/>
+      <c r="T15" s="64"/>
+      <c r="U15" s="64"/>
+      <c r="V15" s="64"/>
+      <c r="W15" s="64"/>
+      <c r="X15" s="64"/>
+      <c r="Y15" s="64"/>
+      <c r="Z15" s="64"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="66" t="s">
+      <c r="B16" s="62" t="s">
         <v>57</v>
       </c>
-      <c r="C16" s="66" t="s">
-        <v>209</v>
-      </c>
-      <c r="D16" s="66" t="s">
-        <v>210</v>
-      </c>
-      <c r="E16" s="66" t="s">
-        <v>211</v>
-      </c>
-      <c r="F16" s="66" t="s">
-        <v>212</v>
-      </c>
-      <c r="G16" s="66" t="s">
-        <v>166</v>
-      </c>
-      <c r="H16" s="68"/>
-      <c r="I16" s="68"/>
-      <c r="J16" s="68"/>
-      <c r="K16" s="68"/>
-      <c r="L16" s="68"/>
-      <c r="M16" s="68"/>
-      <c r="N16" s="68"/>
-      <c r="O16" s="68"/>
-      <c r="P16" s="68"/>
-      <c r="Q16" s="68"/>
-      <c r="R16" s="68"/>
-      <c r="S16" s="68"/>
-      <c r="T16" s="68"/>
-      <c r="U16" s="68"/>
-      <c r="V16" s="68"/>
-      <c r="W16" s="68"/>
-      <c r="X16" s="68"/>
-      <c r="Y16" s="68"/>
-      <c r="Z16" s="68"/>
+      <c r="C16" s="62" t="s">
+        <v>248</v>
+      </c>
+      <c r="D16" s="62" t="s">
+        <v>249</v>
+      </c>
+      <c r="E16" s="62" t="s">
+        <v>250</v>
+      </c>
+      <c r="F16" s="62" t="s">
+        <v>251</v>
+      </c>
+      <c r="G16" s="62" t="s">
+        <v>205</v>
+      </c>
+      <c r="H16" s="64"/>
+      <c r="I16" s="64"/>
+      <c r="J16" s="64"/>
+      <c r="K16" s="64"/>
+      <c r="L16" s="64"/>
+      <c r="M16" s="64"/>
+      <c r="N16" s="64"/>
+      <c r="O16" s="64"/>
+      <c r="P16" s="64"/>
+      <c r="Q16" s="64"/>
+      <c r="R16" s="64"/>
+      <c r="S16" s="64"/>
+      <c r="T16" s="64"/>
+      <c r="U16" s="64"/>
+      <c r="V16" s="64"/>
+      <c r="W16" s="64"/>
+      <c r="X16" s="64"/>
+      <c r="Y16" s="64"/>
+      <c r="Z16" s="64"/>
     </row>
     <row r="17">
       <c r="A17" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="B17" s="66" t="s">
+      <c r="B17" s="62" t="s">
         <v>60</v>
       </c>
-      <c r="C17" s="66" t="s">
-        <v>213</v>
-      </c>
-      <c r="D17" s="66" t="s">
-        <v>214</v>
-      </c>
-      <c r="E17" s="66" t="s">
-        <v>215</v>
-      </c>
-      <c r="F17" s="66" t="s">
-        <v>215</v>
-      </c>
-      <c r="G17" s="66" t="s">
-        <v>166</v>
-      </c>
-      <c r="H17" s="68"/>
-      <c r="I17" s="68"/>
-      <c r="J17" s="68"/>
-      <c r="K17" s="68"/>
-      <c r="L17" s="68"/>
-      <c r="M17" s="68"/>
-      <c r="N17" s="68"/>
-      <c r="O17" s="68"/>
-      <c r="P17" s="68"/>
-      <c r="Q17" s="68"/>
-      <c r="R17" s="68"/>
-      <c r="S17" s="68"/>
-      <c r="T17" s="68"/>
-      <c r="U17" s="68"/>
-      <c r="V17" s="68"/>
-      <c r="W17" s="68"/>
-      <c r="X17" s="68"/>
-      <c r="Y17" s="68"/>
-      <c r="Z17" s="68"/>
+      <c r="C17" s="62" t="s">
+        <v>252</v>
+      </c>
+      <c r="D17" s="62" t="s">
+        <v>253</v>
+      </c>
+      <c r="E17" s="62" t="s">
+        <v>254</v>
+      </c>
+      <c r="F17" s="62" t="s">
+        <v>254</v>
+      </c>
+      <c r="G17" s="62" t="s">
+        <v>205</v>
+      </c>
+      <c r="H17" s="64"/>
+      <c r="I17" s="64"/>
+      <c r="J17" s="64"/>
+      <c r="K17" s="64"/>
+      <c r="L17" s="64"/>
+      <c r="M17" s="64"/>
+      <c r="N17" s="64"/>
+      <c r="O17" s="64"/>
+      <c r="P17" s="64"/>
+      <c r="Q17" s="64"/>
+      <c r="R17" s="64"/>
+      <c r="S17" s="64"/>
+      <c r="T17" s="64"/>
+      <c r="U17" s="64"/>
+      <c r="V17" s="64"/>
+      <c r="W17" s="64"/>
+      <c r="X17" s="64"/>
+      <c r="Y17" s="64"/>
+      <c r="Z17" s="64"/>
     </row>
     <row r="18">
       <c r="A18" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="B18" s="66" t="s">
+      <c r="B18" s="62" t="s">
         <v>63</v>
       </c>
-      <c r="C18" s="66" t="s">
-        <v>216</v>
-      </c>
-      <c r="D18" s="66" t="s">
-        <v>217</v>
-      </c>
-      <c r="E18" s="66" t="s">
-        <v>218</v>
-      </c>
-      <c r="F18" s="66" t="s">
+      <c r="C18" s="62" t="s">
+        <v>255</v>
+      </c>
+      <c r="D18" s="62" t="s">
+        <v>256</v>
+      </c>
+      <c r="E18" s="62" t="s">
+        <v>257</v>
+      </c>
+      <c r="F18" s="62" t="s">
         <v>65</v>
       </c>
-      <c r="G18" s="71" t="s">
-        <v>174</v>
-      </c>
-      <c r="H18" s="68"/>
-      <c r="I18" s="68"/>
-      <c r="J18" s="68"/>
-      <c r="K18" s="68"/>
-      <c r="L18" s="68"/>
-      <c r="M18" s="68"/>
-      <c r="N18" s="68"/>
-      <c r="O18" s="68"/>
-      <c r="P18" s="68"/>
-      <c r="Q18" s="68"/>
-      <c r="R18" s="68"/>
-      <c r="S18" s="68"/>
-      <c r="T18" s="68"/>
-      <c r="U18" s="68"/>
-      <c r="V18" s="68"/>
-      <c r="W18" s="68"/>
-      <c r="X18" s="68"/>
-      <c r="Y18" s="68"/>
-      <c r="Z18" s="68"/>
+      <c r="G18" s="67" t="s">
+        <v>213</v>
+      </c>
+      <c r="H18" s="64"/>
+      <c r="I18" s="64"/>
+      <c r="J18" s="64"/>
+      <c r="K18" s="64"/>
+      <c r="L18" s="64"/>
+      <c r="M18" s="64"/>
+      <c r="N18" s="64"/>
+      <c r="O18" s="64"/>
+      <c r="P18" s="64"/>
+      <c r="Q18" s="64"/>
+      <c r="R18" s="64"/>
+      <c r="S18" s="64"/>
+      <c r="T18" s="64"/>
+      <c r="U18" s="64"/>
+      <c r="V18" s="64"/>
+      <c r="W18" s="64"/>
+      <c r="X18" s="64"/>
+      <c r="Y18" s="64"/>
+      <c r="Z18" s="64"/>
     </row>
     <row r="19">
       <c r="A19" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="B19" s="66" t="s">
+      <c r="B19" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="C19" s="66" t="s">
-        <v>219</v>
-      </c>
-      <c r="D19" s="66" t="s">
-        <v>220</v>
-      </c>
-      <c r="E19" s="66" t="s">
-        <v>221</v>
-      </c>
-      <c r="F19" s="66" t="s">
-        <v>221</v>
-      </c>
-      <c r="G19" s="66" t="s">
-        <v>166</v>
-      </c>
-      <c r="H19" s="68"/>
-      <c r="I19" s="68"/>
-      <c r="J19" s="68"/>
-      <c r="K19" s="68"/>
-      <c r="L19" s="68"/>
-      <c r="M19" s="68"/>
-      <c r="N19" s="68"/>
-      <c r="O19" s="68"/>
-      <c r="P19" s="68"/>
-      <c r="Q19" s="68"/>
-      <c r="R19" s="68"/>
-      <c r="S19" s="68"/>
-      <c r="T19" s="68"/>
-      <c r="U19" s="68"/>
-      <c r="V19" s="68"/>
-      <c r="W19" s="68"/>
-      <c r="X19" s="68"/>
-      <c r="Y19" s="68"/>
-      <c r="Z19" s="68"/>
+      <c r="C19" s="62" t="s">
+        <v>258</v>
+      </c>
+      <c r="D19" s="62" t="s">
+        <v>259</v>
+      </c>
+      <c r="E19" s="62" t="s">
+        <v>260</v>
+      </c>
+      <c r="F19" s="62" t="s">
+        <v>260</v>
+      </c>
+      <c r="G19" s="62" t="s">
+        <v>205</v>
+      </c>
+      <c r="H19" s="64"/>
+      <c r="I19" s="64"/>
+      <c r="J19" s="64"/>
+      <c r="K19" s="64"/>
+      <c r="L19" s="64"/>
+      <c r="M19" s="64"/>
+      <c r="N19" s="64"/>
+      <c r="O19" s="64"/>
+      <c r="P19" s="64"/>
+      <c r="Q19" s="64"/>
+      <c r="R19" s="64"/>
+      <c r="S19" s="64"/>
+      <c r="T19" s="64"/>
+      <c r="U19" s="64"/>
+      <c r="V19" s="64"/>
+      <c r="W19" s="64"/>
+      <c r="X19" s="64"/>
+      <c r="Y19" s="64"/>
+      <c r="Z19" s="64"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -8685,831 +8871,879 @@
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1">
-      <c r="A1" s="61" t="s">
-        <v>222</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="61" t="s">
-        <v>223</v>
-      </c>
-      <c r="D1" s="62"/>
-      <c r="E1" s="63" t="s">
-        <v>224</v>
-      </c>
-      <c r="F1" s="63" t="s">
-        <v>155</v>
-      </c>
-      <c r="G1" s="64"/>
+      <c r="A1" s="56" t="s">
+        <v>261</v>
+      </c>
+      <c r="B1" s="57"/>
+      <c r="C1" s="56" t="s">
+        <v>262</v>
+      </c>
+      <c r="D1" s="57"/>
+      <c r="E1" s="58" t="s">
+        <v>263</v>
+      </c>
+      <c r="F1" s="58" t="s">
+        <v>194</v>
+      </c>
+      <c r="G1" s="59"/>
     </row>
     <row r="2">
-      <c r="A2" s="65" t="s">
-        <v>156</v>
-      </c>
-      <c r="B2" s="65" t="s">
+      <c r="A2" s="60" t="s">
+        <v>195</v>
+      </c>
+      <c r="B2" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="65" t="s">
-        <v>157</v>
-      </c>
-      <c r="D2" s="65" t="s">
-        <v>158</v>
-      </c>
-      <c r="E2" s="65" t="s">
-        <v>159</v>
-      </c>
-      <c r="F2" s="65" t="s">
-        <v>160</v>
-      </c>
-      <c r="G2" s="65" t="s">
-        <v>161</v>
+      <c r="C2" s="60" t="s">
+        <v>196</v>
+      </c>
+      <c r="D2" s="60" t="s">
+        <v>197</v>
+      </c>
+      <c r="E2" s="60" t="s">
+        <v>198</v>
+      </c>
+      <c r="F2" s="60" t="s">
+        <v>199</v>
+      </c>
+      <c r="G2" s="60" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="3" ht="77.25" customHeight="1">
-      <c r="A3" s="67"/>
-      <c r="B3" s="72" t="s">
+      <c r="A3" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="C3" s="72" t="s">
-        <v>225</v>
-      </c>
-      <c r="D3" s="72" t="s">
-        <v>226</v>
-      </c>
-      <c r="E3" s="73" t="s">
-        <v>227</v>
-      </c>
-      <c r="F3" s="73" t="s">
-        <v>227</v>
-      </c>
-      <c r="G3" s="54" t="s">
-        <v>166</v>
-      </c>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="74"/>
-      <c r="K3" s="74"/>
-      <c r="L3" s="74"/>
-      <c r="M3" s="74"/>
-      <c r="N3" s="74"/>
-      <c r="O3" s="74"/>
-      <c r="P3" s="74"/>
-      <c r="Q3" s="74"/>
-      <c r="R3" s="74"/>
+      <c r="B3" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="68" t="s">
+        <v>264</v>
+      </c>
+      <c r="D3" s="68" t="s">
+        <v>265</v>
+      </c>
+      <c r="E3" s="69" t="s">
+        <v>266</v>
+      </c>
+      <c r="F3" s="69" t="s">
+        <v>266</v>
+      </c>
+      <c r="G3" s="50" t="s">
+        <v>205</v>
+      </c>
+      <c r="H3" s="70"/>
+      <c r="I3" s="70"/>
+      <c r="J3" s="70"/>
+      <c r="K3" s="70"/>
+      <c r="L3" s="70"/>
+      <c r="M3" s="70"/>
+      <c r="N3" s="70"/>
+      <c r="O3" s="70"/>
+      <c r="P3" s="70"/>
+      <c r="Q3" s="70"/>
+      <c r="R3" s="70"/>
     </row>
     <row r="4">
-      <c r="A4" s="67"/>
-      <c r="B4" s="72" t="s">
-        <v>74</v>
-      </c>
-      <c r="C4" s="72" t="s">
-        <v>228</v>
-      </c>
-      <c r="D4" s="72" t="s">
-        <v>229</v>
-      </c>
-      <c r="E4" s="73" t="s">
-        <v>230</v>
-      </c>
-      <c r="F4" s="73" t="s">
-        <v>230</v>
-      </c>
-      <c r="G4" s="54" t="s">
-        <v>166</v>
-      </c>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="74"/>
-      <c r="K4" s="74"/>
-      <c r="L4" s="74"/>
-      <c r="M4" s="74"/>
-      <c r="N4" s="74"/>
-      <c r="O4" s="74"/>
-      <c r="P4" s="74"/>
-      <c r="Q4" s="74"/>
-      <c r="R4" s="74"/>
+      <c r="A4" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="68" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="68" t="s">
+        <v>267</v>
+      </c>
+      <c r="D4" s="68" t="s">
+        <v>268</v>
+      </c>
+      <c r="E4" s="69" t="s">
+        <v>269</v>
+      </c>
+      <c r="F4" s="69" t="s">
+        <v>269</v>
+      </c>
+      <c r="G4" s="50" t="s">
+        <v>205</v>
+      </c>
+      <c r="H4" s="70"/>
+      <c r="I4" s="70"/>
+      <c r="J4" s="70"/>
+      <c r="K4" s="70"/>
+      <c r="L4" s="70"/>
+      <c r="M4" s="70"/>
+      <c r="N4" s="70"/>
+      <c r="O4" s="70"/>
+      <c r="P4" s="70"/>
+      <c r="Q4" s="70"/>
+      <c r="R4" s="70"/>
     </row>
     <row r="5">
-      <c r="A5" s="67"/>
-      <c r="B5" s="72" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" s="72" t="s">
-        <v>231</v>
-      </c>
-      <c r="D5" s="72" t="s">
-        <v>232</v>
-      </c>
-      <c r="E5" s="73" t="s">
-        <v>233</v>
-      </c>
-      <c r="F5" s="73" t="s">
-        <v>233</v>
-      </c>
-      <c r="G5" s="54" t="s">
-        <v>166</v>
-      </c>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
-      <c r="K5" s="74"/>
-      <c r="L5" s="74"/>
-      <c r="M5" s="74"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
+      <c r="A5" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5" s="68" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" s="68" t="s">
+        <v>270</v>
+      </c>
+      <c r="D5" s="68" t="s">
+        <v>271</v>
+      </c>
+      <c r="E5" s="69" t="s">
+        <v>272</v>
+      </c>
+      <c r="F5" s="69" t="s">
+        <v>272</v>
+      </c>
+      <c r="G5" s="50" t="s">
+        <v>205</v>
+      </c>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="70"/>
+      <c r="K5" s="70"/>
+      <c r="L5" s="70"/>
+      <c r="M5" s="70"/>
+      <c r="N5" s="70"/>
+      <c r="O5" s="70"/>
+      <c r="P5" s="70"/>
+      <c r="Q5" s="70"/>
+      <c r="R5" s="70"/>
     </row>
     <row r="6">
-      <c r="A6" s="67"/>
-      <c r="B6" s="72" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="72" t="s">
-        <v>234</v>
-      </c>
-      <c r="D6" s="72" t="s">
-        <v>235</v>
-      </c>
-      <c r="E6" s="73" t="s">
-        <v>236</v>
-      </c>
-      <c r="F6" s="73" t="s">
-        <v>236</v>
-      </c>
-      <c r="G6" s="54" t="s">
-        <v>237</v>
-      </c>
-      <c r="H6" s="74"/>
-      <c r="I6" s="74"/>
-      <c r="J6" s="74"/>
-      <c r="K6" s="74"/>
-      <c r="L6" s="74"/>
-      <c r="M6" s="74"/>
-      <c r="N6" s="74"/>
-      <c r="O6" s="74"/>
-      <c r="P6" s="74"/>
-      <c r="Q6" s="74"/>
-      <c r="R6" s="74"/>
+      <c r="A6" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" s="68" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" s="68" t="s">
+        <v>273</v>
+      </c>
+      <c r="D6" s="68" t="s">
+        <v>274</v>
+      </c>
+      <c r="E6" s="69" t="s">
+        <v>275</v>
+      </c>
+      <c r="F6" s="69" t="s">
+        <v>275</v>
+      </c>
+      <c r="G6" s="50" t="s">
+        <v>276</v>
+      </c>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="70"/>
+      <c r="L6" s="70"/>
+      <c r="M6" s="70"/>
+      <c r="N6" s="70"/>
+      <c r="O6" s="70"/>
+      <c r="P6" s="70"/>
+      <c r="Q6" s="70"/>
+      <c r="R6" s="70"/>
     </row>
     <row r="7">
-      <c r="A7" s="67"/>
-      <c r="B7" s="73" t="s">
-        <v>80</v>
-      </c>
-      <c r="C7" s="72" t="s">
-        <v>238</v>
-      </c>
-      <c r="D7" s="72" t="s">
-        <v>239</v>
-      </c>
-      <c r="E7" s="75" t="s">
-        <v>240</v>
-      </c>
-      <c r="F7" s="75" t="s">
-        <v>240</v>
-      </c>
-      <c r="G7" s="54" t="s">
-        <v>237</v>
-      </c>
-      <c r="H7" s="74"/>
-      <c r="I7" s="74"/>
-      <c r="J7" s="74"/>
-      <c r="K7" s="74"/>
-      <c r="L7" s="74"/>
-      <c r="M7" s="74"/>
-      <c r="N7" s="74"/>
-      <c r="O7" s="74"/>
-      <c r="P7" s="74"/>
-      <c r="Q7" s="74"/>
-      <c r="R7" s="74"/>
+      <c r="A7" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" s="69" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" s="68" t="s">
+        <v>277</v>
+      </c>
+      <c r="D7" s="68" t="s">
+        <v>278</v>
+      </c>
+      <c r="E7" s="71" t="s">
+        <v>279</v>
+      </c>
+      <c r="F7" s="71" t="s">
+        <v>279</v>
+      </c>
+      <c r="G7" s="50" t="s">
+        <v>276</v>
+      </c>
+      <c r="H7" s="70"/>
+      <c r="I7" s="70"/>
+      <c r="J7" s="70"/>
+      <c r="K7" s="70"/>
+      <c r="L7" s="70"/>
+      <c r="M7" s="70"/>
+      <c r="N7" s="70"/>
+      <c r="O7" s="70"/>
+      <c r="P7" s="70"/>
+      <c r="Q7" s="70"/>
+      <c r="R7" s="70"/>
     </row>
     <row r="8">
-      <c r="A8" s="67"/>
-      <c r="B8" s="73" t="s">
-        <v>82</v>
-      </c>
-      <c r="C8" s="72" t="s">
-        <v>241</v>
-      </c>
-      <c r="D8" s="72" t="s">
-        <v>242</v>
-      </c>
-      <c r="E8" s="73" t="s">
-        <v>243</v>
-      </c>
-      <c r="F8" s="73" t="s">
-        <v>243</v>
-      </c>
-      <c r="G8" s="54" t="s">
-        <v>237</v>
-      </c>
-      <c r="H8" s="74"/>
-      <c r="I8" s="74"/>
-      <c r="J8" s="74"/>
-      <c r="K8" s="74"/>
-      <c r="L8" s="74"/>
-      <c r="M8" s="74"/>
-      <c r="N8" s="74"/>
-      <c r="O8" s="74"/>
-      <c r="P8" s="74"/>
-      <c r="Q8" s="74"/>
-      <c r="R8" s="74"/>
+      <c r="A8" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="B8" s="69" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" s="68" t="s">
+        <v>280</v>
+      </c>
+      <c r="D8" s="68" t="s">
+        <v>281</v>
+      </c>
+      <c r="E8" s="69" t="s">
+        <v>282</v>
+      </c>
+      <c r="F8" s="69" t="s">
+        <v>282</v>
+      </c>
+      <c r="G8" s="50" t="s">
+        <v>276</v>
+      </c>
+      <c r="H8" s="70"/>
+      <c r="I8" s="70"/>
+      <c r="J8" s="70"/>
+      <c r="K8" s="70"/>
+      <c r="L8" s="70"/>
+      <c r="M8" s="70"/>
+      <c r="N8" s="70"/>
+      <c r="O8" s="70"/>
+      <c r="P8" s="70"/>
+      <c r="Q8" s="70"/>
+      <c r="R8" s="70"/>
     </row>
     <row r="9">
-      <c r="A9" s="67"/>
-      <c r="B9" s="73" t="s">
-        <v>84</v>
-      </c>
-      <c r="C9" s="73" t="s">
-        <v>244</v>
-      </c>
-      <c r="D9" s="72" t="s">
-        <v>245</v>
-      </c>
-      <c r="E9" s="73" t="s">
-        <v>85</v>
-      </c>
-      <c r="F9" s="73" t="s">
-        <v>85</v>
-      </c>
-      <c r="G9" s="54" t="s">
-        <v>237</v>
-      </c>
-      <c r="H9" s="74"/>
-      <c r="I9" s="74"/>
-      <c r="J9" s="74"/>
-      <c r="K9" s="74"/>
-      <c r="L9" s="74"/>
-      <c r="M9" s="74"/>
-      <c r="N9" s="74"/>
-      <c r="O9" s="74"/>
-      <c r="P9" s="74"/>
-      <c r="Q9" s="74"/>
-      <c r="R9" s="74"/>
+      <c r="A9" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="69" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" s="69" t="s">
+        <v>283</v>
+      </c>
+      <c r="D9" s="68" t="s">
+        <v>284</v>
+      </c>
+      <c r="E9" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="F9" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="G9" s="50" t="s">
+        <v>276</v>
+      </c>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="70"/>
+      <c r="K9" s="70"/>
+      <c r="L9" s="70"/>
+      <c r="M9" s="70"/>
+      <c r="N9" s="70"/>
+      <c r="O9" s="70"/>
+      <c r="P9" s="70"/>
+      <c r="Q9" s="70"/>
+      <c r="R9" s="70"/>
     </row>
     <row r="10">
-      <c r="A10" s="67"/>
-      <c r="B10" s="73" t="s">
-        <v>86</v>
-      </c>
-      <c r="C10" s="72" t="s">
-        <v>246</v>
-      </c>
-      <c r="D10" s="73" t="s">
-        <v>247</v>
-      </c>
-      <c r="E10" s="73" t="s">
-        <v>248</v>
-      </c>
-      <c r="F10" s="73" t="s">
-        <v>248</v>
-      </c>
-      <c r="G10" s="54" t="s">
-        <v>237</v>
-      </c>
-      <c r="H10" s="74"/>
-      <c r="I10" s="74"/>
-      <c r="J10" s="74"/>
-      <c r="K10" s="74"/>
-      <c r="L10" s="74"/>
-      <c r="M10" s="74"/>
-      <c r="N10" s="74"/>
-      <c r="O10" s="74"/>
-      <c r="P10" s="74"/>
-      <c r="Q10" s="74"/>
-      <c r="R10" s="74"/>
+      <c r="A10" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="B10" s="69" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="D10" s="69" t="s">
+        <v>286</v>
+      </c>
+      <c r="E10" s="69" t="s">
+        <v>287</v>
+      </c>
+      <c r="F10" s="69" t="s">
+        <v>287</v>
+      </c>
+      <c r="G10" s="50" t="s">
+        <v>276</v>
+      </c>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="70"/>
+      <c r="K10" s="70"/>
+      <c r="L10" s="70"/>
+      <c r="M10" s="70"/>
+      <c r="N10" s="70"/>
+      <c r="O10" s="70"/>
+      <c r="P10" s="70"/>
+      <c r="Q10" s="70"/>
+      <c r="R10" s="70"/>
     </row>
     <row r="11">
-      <c r="A11" s="67"/>
-      <c r="B11" s="73" t="s">
-        <v>88</v>
-      </c>
-      <c r="C11" s="73" t="s">
-        <v>249</v>
-      </c>
-      <c r="D11" s="73" t="s">
-        <v>250</v>
-      </c>
-      <c r="E11" s="73" t="s">
-        <v>251</v>
-      </c>
-      <c r="F11" s="75" t="s">
-        <v>252</v>
-      </c>
-      <c r="G11" s="54" t="s">
-        <v>237</v>
-      </c>
-      <c r="H11" s="74"/>
-      <c r="I11" s="74"/>
-      <c r="J11" s="74"/>
-      <c r="K11" s="74"/>
-      <c r="L11" s="74"/>
-      <c r="M11" s="74"/>
-      <c r="N11" s="74"/>
-      <c r="O11" s="74"/>
-      <c r="P11" s="74"/>
-      <c r="Q11" s="74"/>
-      <c r="R11" s="74"/>
+      <c r="A11" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="B11" s="69" t="s">
+        <v>97</v>
+      </c>
+      <c r="C11" s="69" t="s">
+        <v>288</v>
+      </c>
+      <c r="D11" s="69" t="s">
+        <v>289</v>
+      </c>
+      <c r="E11" s="69" t="s">
+        <v>290</v>
+      </c>
+      <c r="F11" s="71" t="s">
+        <v>291</v>
+      </c>
+      <c r="G11" s="50" t="s">
+        <v>276</v>
+      </c>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="70"/>
+      <c r="K11" s="70"/>
+      <c r="L11" s="70"/>
+      <c r="M11" s="70"/>
+      <c r="N11" s="70"/>
+      <c r="O11" s="70"/>
+      <c r="P11" s="70"/>
+      <c r="Q11" s="70"/>
+      <c r="R11" s="70"/>
     </row>
     <row r="12">
-      <c r="A12" s="67"/>
-      <c r="B12" s="73" t="s">
-        <v>90</v>
-      </c>
-      <c r="C12" s="73" t="s">
-        <v>253</v>
-      </c>
-      <c r="D12" s="73" t="s">
-        <v>254</v>
-      </c>
-      <c r="E12" s="73" t="s">
-        <v>255</v>
-      </c>
-      <c r="F12" s="73" t="s">
-        <v>85</v>
-      </c>
-      <c r="G12" s="54" t="s">
-        <v>237</v>
-      </c>
-      <c r="H12" s="74"/>
-      <c r="I12" s="74"/>
-      <c r="J12" s="74"/>
-      <c r="K12" s="74"/>
-      <c r="L12" s="74"/>
-      <c r="M12" s="74"/>
-      <c r="N12" s="74"/>
-      <c r="O12" s="74"/>
-      <c r="P12" s="74"/>
-      <c r="Q12" s="74"/>
-      <c r="R12" s="74"/>
+      <c r="A12" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="B12" s="69" t="s">
+        <v>100</v>
+      </c>
+      <c r="C12" s="69" t="s">
+        <v>292</v>
+      </c>
+      <c r="D12" s="69" t="s">
+        <v>293</v>
+      </c>
+      <c r="E12" s="69" t="s">
+        <v>294</v>
+      </c>
+      <c r="F12" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="G12" s="50" t="s">
+        <v>276</v>
+      </c>
+      <c r="H12" s="70"/>
+      <c r="I12" s="70"/>
+      <c r="J12" s="70"/>
+      <c r="K12" s="70"/>
+      <c r="L12" s="70"/>
+      <c r="M12" s="70"/>
+      <c r="N12" s="70"/>
+      <c r="O12" s="70"/>
+      <c r="P12" s="70"/>
+      <c r="Q12" s="70"/>
+      <c r="R12" s="70"/>
     </row>
     <row r="13">
-      <c r="A13" s="67"/>
-      <c r="B13" s="72" t="s">
-        <v>92</v>
-      </c>
-      <c r="C13" s="72" t="s">
-        <v>256</v>
-      </c>
-      <c r="D13" s="72" t="s">
-        <v>257</v>
-      </c>
-      <c r="E13" s="73" t="s">
-        <v>258</v>
-      </c>
-      <c r="F13" s="75" t="s">
-        <v>259</v>
-      </c>
-      <c r="G13" s="54" t="s">
-        <v>237</v>
-      </c>
-      <c r="H13" s="74"/>
-      <c r="I13" s="74"/>
-      <c r="J13" s="74"/>
-      <c r="K13" s="74"/>
-      <c r="L13" s="74"/>
-      <c r="M13" s="74"/>
-      <c r="N13" s="74"/>
-      <c r="O13" s="74"/>
-      <c r="P13" s="74"/>
-      <c r="Q13" s="74"/>
-      <c r="R13" s="74"/>
+      <c r="A13" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="B13" s="68" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="68" t="s">
+        <v>295</v>
+      </c>
+      <c r="D13" s="68" t="s">
+        <v>296</v>
+      </c>
+      <c r="E13" s="69" t="s">
+        <v>297</v>
+      </c>
+      <c r="F13" s="71" t="s">
+        <v>298</v>
+      </c>
+      <c r="G13" s="50" t="s">
+        <v>276</v>
+      </c>
+      <c r="H13" s="70"/>
+      <c r="I13" s="70"/>
+      <c r="J13" s="70"/>
+      <c r="K13" s="70"/>
+      <c r="L13" s="70"/>
+      <c r="M13" s="70"/>
+      <c r="N13" s="70"/>
+      <c r="O13" s="70"/>
+      <c r="P13" s="70"/>
+      <c r="Q13" s="70"/>
+      <c r="R13" s="70"/>
     </row>
     <row r="14">
-      <c r="A14" s="67"/>
-      <c r="B14" s="72" t="s">
-        <v>94</v>
-      </c>
-      <c r="C14" s="72" t="s">
-        <v>260</v>
-      </c>
-      <c r="D14" s="72" t="s">
-        <v>261</v>
-      </c>
-      <c r="E14" s="73" t="s">
-        <v>262</v>
-      </c>
-      <c r="F14" s="75" t="s">
-        <v>263</v>
-      </c>
-      <c r="G14" s="54" t="s">
-        <v>237</v>
-      </c>
-      <c r="H14" s="74"/>
-      <c r="I14" s="74"/>
-      <c r="J14" s="74"/>
-      <c r="K14" s="74"/>
-      <c r="L14" s="74"/>
-      <c r="M14" s="74"/>
-      <c r="N14" s="74"/>
-      <c r="O14" s="74"/>
-      <c r="P14" s="74"/>
-      <c r="Q14" s="74"/>
-      <c r="R14" s="74"/>
+      <c r="A14" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="B14" s="68" t="s">
+        <v>106</v>
+      </c>
+      <c r="C14" s="68" t="s">
+        <v>299</v>
+      </c>
+      <c r="D14" s="68" t="s">
+        <v>300</v>
+      </c>
+      <c r="E14" s="69" t="s">
+        <v>301</v>
+      </c>
+      <c r="F14" s="71" t="s">
+        <v>302</v>
+      </c>
+      <c r="G14" s="50" t="s">
+        <v>276</v>
+      </c>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="70"/>
+      <c r="K14" s="70"/>
+      <c r="L14" s="70"/>
+      <c r="M14" s="70"/>
+      <c r="N14" s="70"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="70"/>
+      <c r="Q14" s="70"/>
+      <c r="R14" s="70"/>
     </row>
     <row r="15">
-      <c r="A15" s="67"/>
-      <c r="B15" s="72" t="s">
-        <v>96</v>
-      </c>
-      <c r="C15" s="72" t="s">
-        <v>264</v>
-      </c>
-      <c r="D15" s="72" t="s">
-        <v>265</v>
-      </c>
-      <c r="E15" s="73" t="s">
-        <v>266</v>
-      </c>
-      <c r="F15" s="75" t="s">
-        <v>267</v>
-      </c>
-      <c r="G15" s="54" t="s">
-        <v>237</v>
-      </c>
-      <c r="H15" s="74"/>
-      <c r="I15" s="74"/>
-      <c r="J15" s="74"/>
-      <c r="K15" s="74"/>
-      <c r="L15" s="74"/>
-      <c r="M15" s="74"/>
-      <c r="N15" s="74"/>
-      <c r="O15" s="74"/>
-      <c r="P15" s="74"/>
-      <c r="Q15" s="74"/>
-      <c r="R15" s="74"/>
+      <c r="A15" s="33" t="s">
+        <v>108</v>
+      </c>
+      <c r="B15" s="68" t="s">
+        <v>109</v>
+      </c>
+      <c r="C15" s="68" t="s">
+        <v>303</v>
+      </c>
+      <c r="D15" s="68" t="s">
+        <v>304</v>
+      </c>
+      <c r="E15" s="69" t="s">
+        <v>305</v>
+      </c>
+      <c r="F15" s="71" t="s">
+        <v>306</v>
+      </c>
+      <c r="G15" s="50" t="s">
+        <v>276</v>
+      </c>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="70"/>
+      <c r="K15" s="70"/>
+      <c r="L15" s="70"/>
+      <c r="M15" s="70"/>
+      <c r="N15" s="70"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="70"/>
+      <c r="Q15" s="70"/>
+      <c r="R15" s="70"/>
     </row>
     <row r="16">
-      <c r="A16" s="67"/>
-      <c r="B16" s="72" t="s">
-        <v>98</v>
-      </c>
-      <c r="C16" s="72" t="s">
-        <v>268</v>
-      </c>
-      <c r="D16" s="72" t="s">
-        <v>269</v>
-      </c>
-      <c r="E16" s="73" t="s">
-        <v>270</v>
-      </c>
-      <c r="F16" s="76" t="s">
-        <v>271</v>
-      </c>
-      <c r="G16" s="54" t="s">
-        <v>237</v>
-      </c>
-      <c r="H16" s="74"/>
-      <c r="I16" s="74"/>
-      <c r="J16" s="74"/>
-      <c r="K16" s="74"/>
-      <c r="L16" s="74"/>
-      <c r="M16" s="74"/>
-      <c r="N16" s="74"/>
-      <c r="O16" s="74"/>
-      <c r="P16" s="74"/>
-      <c r="Q16" s="74"/>
-      <c r="R16" s="74"/>
+      <c r="A16" s="33" t="s">
+        <v>111</v>
+      </c>
+      <c r="B16" s="68" t="s">
+        <v>112</v>
+      </c>
+      <c r="C16" s="68" t="s">
+        <v>307</v>
+      </c>
+      <c r="D16" s="68" t="s">
+        <v>308</v>
+      </c>
+      <c r="E16" s="69" t="s">
+        <v>309</v>
+      </c>
+      <c r="F16" s="72" t="s">
+        <v>310</v>
+      </c>
+      <c r="G16" s="50" t="s">
+        <v>276</v>
+      </c>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="70"/>
+      <c r="K16" s="70"/>
+      <c r="L16" s="70"/>
+      <c r="M16" s="70"/>
+      <c r="N16" s="70"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="70"/>
+      <c r="Q16" s="70"/>
+      <c r="R16" s="70"/>
     </row>
     <row r="17">
-      <c r="A17" s="67"/>
-      <c r="B17" s="72" t="s">
-        <v>100</v>
-      </c>
-      <c r="C17" s="72" t="s">
-        <v>272</v>
-      </c>
-      <c r="D17" s="72" t="s">
-        <v>273</v>
-      </c>
-      <c r="E17" s="73" t="s">
-        <v>274</v>
-      </c>
-      <c r="F17" s="76" t="s">
-        <v>275</v>
-      </c>
-      <c r="G17" s="54" t="s">
-        <v>237</v>
-      </c>
-      <c r="H17" s="74"/>
-      <c r="I17" s="74"/>
-      <c r="J17" s="74"/>
-      <c r="K17" s="74"/>
-      <c r="L17" s="74"/>
-      <c r="M17" s="74"/>
-      <c r="N17" s="74"/>
-      <c r="O17" s="74"/>
-      <c r="P17" s="74"/>
-      <c r="Q17" s="74"/>
-      <c r="R17" s="74"/>
+      <c r="A17" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="B17" s="68" t="s">
+        <v>115</v>
+      </c>
+      <c r="C17" s="68" t="s">
+        <v>311</v>
+      </c>
+      <c r="D17" s="68" t="s">
+        <v>312</v>
+      </c>
+      <c r="E17" s="69" t="s">
+        <v>313</v>
+      </c>
+      <c r="F17" s="72" t="s">
+        <v>314</v>
+      </c>
+      <c r="G17" s="50" t="s">
+        <v>276</v>
+      </c>
+      <c r="H17" s="70"/>
+      <c r="I17" s="70"/>
+      <c r="J17" s="70"/>
+      <c r="K17" s="70"/>
+      <c r="L17" s="70"/>
+      <c r="M17" s="70"/>
+      <c r="N17" s="70"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="70"/>
+      <c r="Q17" s="70"/>
+      <c r="R17" s="70"/>
     </row>
     <row r="18">
-      <c r="A18" s="67"/>
-      <c r="B18" s="72" t="s">
-        <v>102</v>
-      </c>
-      <c r="C18" s="72" t="s">
+      <c r="A18" s="33" t="s">
+        <v>117</v>
+      </c>
+      <c r="B18" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="C18" s="68" t="s">
+        <v>315</v>
+      </c>
+      <c r="D18" s="68" t="s">
+        <v>316</v>
+      </c>
+      <c r="E18" s="69" t="s">
+        <v>317</v>
+      </c>
+      <c r="F18" s="73" t="s">
+        <v>318</v>
+      </c>
+      <c r="G18" s="50" t="s">
         <v>276</v>
       </c>
-      <c r="D18" s="72" t="s">
-        <v>277</v>
-      </c>
-      <c r="E18" s="73" t="s">
-        <v>278</v>
-      </c>
-      <c r="F18" s="77" t="s">
-        <v>279</v>
-      </c>
-      <c r="G18" s="54" t="s">
-        <v>237</v>
-      </c>
-      <c r="H18" s="74"/>
-      <c r="I18" s="74"/>
-      <c r="J18" s="74"/>
-      <c r="K18" s="74"/>
-      <c r="L18" s="74"/>
-      <c r="M18" s="74"/>
-      <c r="N18" s="74"/>
-      <c r="O18" s="74"/>
-      <c r="P18" s="74"/>
-      <c r="Q18" s="74"/>
-      <c r="R18" s="74"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="70"/>
+      <c r="K18" s="70"/>
+      <c r="L18" s="70"/>
+      <c r="M18" s="70"/>
+      <c r="N18" s="70"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="70"/>
+      <c r="Q18" s="70"/>
+      <c r="R18" s="70"/>
     </row>
     <row r="19">
-      <c r="A19" s="67"/>
-      <c r="B19" s="72" t="s">
-        <v>104</v>
-      </c>
-      <c r="C19" s="72" t="s">
-        <v>280</v>
-      </c>
-      <c r="D19" s="72" t="s">
-        <v>281</v>
-      </c>
-      <c r="E19" s="73" t="s">
-        <v>282</v>
-      </c>
-      <c r="F19" s="75" t="s">
-        <v>283</v>
-      </c>
-      <c r="G19" s="54" t="s">
-        <v>237</v>
-      </c>
-      <c r="H19" s="74"/>
-      <c r="I19" s="74"/>
-      <c r="J19" s="74"/>
-      <c r="K19" s="74"/>
-      <c r="L19" s="74"/>
-      <c r="M19" s="74"/>
-      <c r="N19" s="74"/>
-      <c r="O19" s="74"/>
-      <c r="P19" s="74"/>
-      <c r="Q19" s="74"/>
-      <c r="R19" s="74"/>
+      <c r="A19" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="B19" s="68" t="s">
+        <v>121</v>
+      </c>
+      <c r="C19" s="68" t="s">
+        <v>319</v>
+      </c>
+      <c r="D19" s="68" t="s">
+        <v>320</v>
+      </c>
+      <c r="E19" s="69" t="s">
+        <v>321</v>
+      </c>
+      <c r="F19" s="71" t="s">
+        <v>322</v>
+      </c>
+      <c r="G19" s="50" t="s">
+        <v>276</v>
+      </c>
+      <c r="H19" s="70"/>
+      <c r="I19" s="70"/>
+      <c r="J19" s="70"/>
+      <c r="K19" s="70"/>
+      <c r="L19" s="70"/>
+      <c r="M19" s="70"/>
+      <c r="N19" s="70"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="70"/>
+      <c r="Q19" s="70"/>
+      <c r="R19" s="70"/>
     </row>
     <row r="20">
-      <c r="A20" s="66"/>
-      <c r="B20" s="72" t="s">
-        <v>106</v>
-      </c>
-      <c r="C20" s="72" t="s">
-        <v>284</v>
-      </c>
-      <c r="D20" s="72" t="s">
-        <v>285</v>
-      </c>
-      <c r="E20" s="73" t="s">
-        <v>286</v>
-      </c>
-      <c r="F20" s="75" t="s">
-        <v>287</v>
-      </c>
-      <c r="G20" s="54" t="s">
-        <v>237</v>
-      </c>
-      <c r="H20" s="74"/>
-      <c r="I20" s="74"/>
-      <c r="J20" s="74"/>
-      <c r="K20" s="74"/>
-      <c r="L20" s="74"/>
-      <c r="M20" s="74"/>
-      <c r="N20" s="74"/>
-      <c r="O20" s="74"/>
-      <c r="P20" s="74"/>
-      <c r="Q20" s="74"/>
-      <c r="R20" s="74"/>
+      <c r="A20" s="33" t="s">
+        <v>123</v>
+      </c>
+      <c r="B20" s="68" t="s">
+        <v>124</v>
+      </c>
+      <c r="C20" s="68" t="s">
+        <v>323</v>
+      </c>
+      <c r="D20" s="68" t="s">
+        <v>324</v>
+      </c>
+      <c r="E20" s="69" t="s">
+        <v>325</v>
+      </c>
+      <c r="F20" s="71" t="s">
+        <v>326</v>
+      </c>
+      <c r="G20" s="50" t="s">
+        <v>276</v>
+      </c>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="70"/>
+      <c r="K20" s="70"/>
+      <c r="L20" s="70"/>
+      <c r="M20" s="70"/>
+      <c r="N20" s="70"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="70"/>
+      <c r="Q20" s="70"/>
+      <c r="R20" s="70"/>
     </row>
     <row r="21">
-      <c r="A21" s="66"/>
-      <c r="B21" s="72" t="s">
-        <v>108</v>
-      </c>
-      <c r="C21" s="72" t="s">
-        <v>288</v>
-      </c>
-      <c r="D21" s="72" t="s">
-        <v>289</v>
-      </c>
-      <c r="E21" s="73" t="s">
-        <v>290</v>
-      </c>
-      <c r="F21" s="75" t="s">
-        <v>291</v>
-      </c>
-      <c r="G21" s="54" t="s">
-        <v>237</v>
-      </c>
-      <c r="H21" s="74"/>
-      <c r="I21" s="74"/>
-      <c r="J21" s="74"/>
-      <c r="K21" s="74"/>
-      <c r="L21" s="74"/>
-      <c r="M21" s="74"/>
-      <c r="N21" s="74"/>
-      <c r="O21" s="74"/>
-      <c r="P21" s="74"/>
-      <c r="Q21" s="74"/>
-      <c r="R21" s="74"/>
+      <c r="A21" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="B21" s="68" t="s">
+        <v>127</v>
+      </c>
+      <c r="C21" s="68" t="s">
+        <v>327</v>
+      </c>
+      <c r="D21" s="68" t="s">
+        <v>328</v>
+      </c>
+      <c r="E21" s="69" t="s">
+        <v>329</v>
+      </c>
+      <c r="F21" s="71" t="s">
+        <v>330</v>
+      </c>
+      <c r="G21" s="50" t="s">
+        <v>276</v>
+      </c>
+      <c r="H21" s="70"/>
+      <c r="I21" s="70"/>
+      <c r="J21" s="70"/>
+      <c r="K21" s="70"/>
+      <c r="L21" s="70"/>
+      <c r="M21" s="70"/>
+      <c r="N21" s="70"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="70"/>
+      <c r="Q21" s="70"/>
+      <c r="R21" s="70"/>
     </row>
     <row r="22">
-      <c r="A22" s="66"/>
-      <c r="B22" s="73" t="s">
-        <v>110</v>
-      </c>
-      <c r="C22" s="73" t="s">
-        <v>292</v>
-      </c>
-      <c r="D22" s="73" t="s">
-        <v>293</v>
-      </c>
-      <c r="E22" s="73" t="s">
-        <v>294</v>
-      </c>
-      <c r="F22" s="76" t="s">
-        <v>295</v>
-      </c>
-      <c r="G22" s="54" t="s">
-        <v>237</v>
-      </c>
-      <c r="H22" s="74"/>
-      <c r="I22" s="74"/>
-      <c r="J22" s="74"/>
-      <c r="K22" s="74"/>
-      <c r="L22" s="74"/>
-      <c r="M22" s="74"/>
-      <c r="N22" s="74"/>
-      <c r="O22" s="74"/>
-      <c r="P22" s="74"/>
-      <c r="Q22" s="74"/>
-      <c r="R22" s="74"/>
+      <c r="A22" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="B22" s="69" t="s">
+        <v>130</v>
+      </c>
+      <c r="C22" s="69" t="s">
+        <v>331</v>
+      </c>
+      <c r="D22" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="E22" s="69" t="s">
+        <v>333</v>
+      </c>
+      <c r="F22" s="72" t="s">
+        <v>334</v>
+      </c>
+      <c r="G22" s="50" t="s">
+        <v>276</v>
+      </c>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70"/>
+      <c r="J22" s="70"/>
+      <c r="K22" s="70"/>
+      <c r="L22" s="70"/>
+      <c r="M22" s="70"/>
+      <c r="N22" s="70"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="70"/>
+      <c r="Q22" s="70"/>
+      <c r="R22" s="70"/>
     </row>
     <row r="23">
-      <c r="A23" s="66"/>
-      <c r="B23" s="73" t="s">
-        <v>112</v>
-      </c>
-      <c r="C23" s="73" t="s">
-        <v>296</v>
-      </c>
-      <c r="D23" s="73" t="s">
-        <v>297</v>
-      </c>
-      <c r="E23" s="73" t="s">
-        <v>298</v>
-      </c>
-      <c r="F23" s="78" t="s">
-        <v>299</v>
-      </c>
-      <c r="G23" s="54" t="s">
-        <v>237</v>
-      </c>
-      <c r="H23" s="74"/>
-      <c r="I23" s="74"/>
-      <c r="J23" s="74"/>
-      <c r="K23" s="74"/>
-      <c r="L23" s="74"/>
-      <c r="M23" s="74"/>
-      <c r="N23" s="74"/>
-      <c r="O23" s="74"/>
-      <c r="P23" s="74"/>
-      <c r="Q23" s="74"/>
-      <c r="R23" s="74"/>
+      <c r="A23" s="33" t="s">
+        <v>132</v>
+      </c>
+      <c r="B23" s="69" t="s">
+        <v>133</v>
+      </c>
+      <c r="C23" s="69" t="s">
+        <v>335</v>
+      </c>
+      <c r="D23" s="69" t="s">
+        <v>336</v>
+      </c>
+      <c r="E23" s="69" t="s">
+        <v>337</v>
+      </c>
+      <c r="F23" s="74" t="s">
+        <v>338</v>
+      </c>
+      <c r="G23" s="50" t="s">
+        <v>276</v>
+      </c>
+      <c r="H23" s="70"/>
+      <c r="I23" s="70"/>
+      <c r="J23" s="70"/>
+      <c r="K23" s="70"/>
+      <c r="L23" s="70"/>
+      <c r="M23" s="70"/>
+      <c r="N23" s="70"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="70"/>
+      <c r="Q23" s="70"/>
+      <c r="R23" s="70"/>
     </row>
     <row r="24">
-      <c r="A24" s="66"/>
-      <c r="B24" s="73" t="s">
-        <v>114</v>
-      </c>
-      <c r="C24" s="73" t="s">
-        <v>300</v>
-      </c>
-      <c r="D24" s="73" t="s">
-        <v>301</v>
-      </c>
-      <c r="E24" s="73" t="s">
-        <v>302</v>
-      </c>
-      <c r="F24" s="78" t="s">
-        <v>303</v>
-      </c>
-      <c r="G24" s="54" t="s">
-        <v>237</v>
-      </c>
-      <c r="H24" s="74"/>
-      <c r="I24" s="74"/>
-      <c r="J24" s="74"/>
-      <c r="K24" s="74"/>
-      <c r="L24" s="74"/>
-      <c r="M24" s="74"/>
-      <c r="N24" s="74"/>
-      <c r="O24" s="74"/>
-      <c r="P24" s="74"/>
-      <c r="Q24" s="74"/>
-      <c r="R24" s="74"/>
+      <c r="A24" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="B24" s="69" t="s">
+        <v>136</v>
+      </c>
+      <c r="C24" s="69" t="s">
+        <v>339</v>
+      </c>
+      <c r="D24" s="69" t="s">
+        <v>340</v>
+      </c>
+      <c r="E24" s="69" t="s">
+        <v>341</v>
+      </c>
+      <c r="F24" s="74" t="s">
+        <v>342</v>
+      </c>
+      <c r="G24" s="50" t="s">
+        <v>276</v>
+      </c>
+      <c r="H24" s="70"/>
+      <c r="I24" s="70"/>
+      <c r="J24" s="70"/>
+      <c r="K24" s="70"/>
+      <c r="L24" s="70"/>
+      <c r="M24" s="70"/>
+      <c r="N24" s="70"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="70"/>
+      <c r="Q24" s="70"/>
+      <c r="R24" s="70"/>
     </row>
     <row r="25">
-      <c r="A25" s="66"/>
-      <c r="B25" s="73" t="s">
-        <v>116</v>
-      </c>
-      <c r="C25" s="73" t="s">
-        <v>304</v>
-      </c>
-      <c r="D25" s="73" t="s">
-        <v>305</v>
-      </c>
-      <c r="E25" s="75" t="s">
-        <v>306</v>
-      </c>
-      <c r="F25" s="79" t="s">
-        <v>307</v>
-      </c>
-      <c r="G25" s="54" t="s">
-        <v>237</v>
-      </c>
-      <c r="H25" s="74"/>
-      <c r="I25" s="74"/>
-      <c r="J25" s="74"/>
-      <c r="K25" s="74"/>
-      <c r="L25" s="74"/>
-      <c r="M25" s="74"/>
-      <c r="N25" s="74"/>
-      <c r="O25" s="74"/>
-      <c r="P25" s="74"/>
-      <c r="Q25" s="74"/>
-      <c r="R25" s="74"/>
+      <c r="A25" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="B25" s="69" t="s">
+        <v>139</v>
+      </c>
+      <c r="C25" s="69" t="s">
+        <v>343</v>
+      </c>
+      <c r="D25" s="69" t="s">
+        <v>344</v>
+      </c>
+      <c r="E25" s="71" t="s">
+        <v>345</v>
+      </c>
+      <c r="F25" s="75" t="s">
+        <v>346</v>
+      </c>
+      <c r="G25" s="50" t="s">
+        <v>276</v>
+      </c>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70"/>
+      <c r="J25" s="70"/>
+      <c r="K25" s="70"/>
+      <c r="L25" s="70"/>
+      <c r="M25" s="70"/>
+      <c r="N25" s="70"/>
+      <c r="O25" s="70"/>
+      <c r="P25" s="70"/>
+      <c r="Q25" s="70"/>
+      <c r="R25" s="70"/>
     </row>
     <row r="26">
-      <c r="A26" s="66"/>
-      <c r="B26" s="73" t="s">
-        <v>118</v>
-      </c>
-      <c r="C26" s="73" t="s">
-        <v>308</v>
-      </c>
-      <c r="D26" s="66" t="s">
-        <v>309</v>
-      </c>
-      <c r="E26" s="73" t="s">
-        <v>310</v>
-      </c>
-      <c r="F26" s="78" t="s">
-        <v>311</v>
-      </c>
-      <c r="G26" s="54" t="s">
-        <v>237</v>
+      <c r="A26" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="B26" s="69" t="s">
+        <v>142</v>
+      </c>
+      <c r="C26" s="69" t="s">
+        <v>347</v>
+      </c>
+      <c r="D26" s="62" t="s">
+        <v>348</v>
+      </c>
+      <c r="E26" s="69" t="s">
+        <v>349</v>
+      </c>
+      <c r="F26" s="74" t="s">
+        <v>350</v>
+      </c>
+      <c r="G26" s="50" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="68"/>
-      <c r="B27" s="80"/>
-      <c r="C27" s="68"/>
-      <c r="D27" s="68"/>
-      <c r="E27" s="68"/>
-      <c r="F27" s="81"/>
+      <c r="A27" s="64"/>
+      <c r="B27" s="76"/>
+      <c r="C27" s="64"/>
+      <c r="D27" s="64"/>
+      <c r="E27" s="64"/>
+      <c r="F27" s="77"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="68"/>
-      <c r="B28" s="80"/>
-      <c r="C28" s="68"/>
-      <c r="D28" s="68"/>
-      <c r="E28" s="68"/>
-      <c r="F28" s="81"/>
+      <c r="A28" s="64"/>
+      <c r="B28" s="76"/>
+      <c r="C28" s="64"/>
+      <c r="D28" s="64"/>
+      <c r="E28" s="64"/>
+      <c r="F28" s="77"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="68"/>
-      <c r="B29" s="80"/>
-      <c r="C29" s="68"/>
-      <c r="D29" s="68"/>
-      <c r="E29" s="68"/>
+      <c r="A29" s="64"/>
+      <c r="B29" s="76"/>
+      <c r="C29" s="64"/>
+      <c r="D29" s="64"/>
+      <c r="E29" s="64"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="68"/>
-      <c r="B30" s="68"/>
-      <c r="C30" s="68"/>
-      <c r="D30" s="68"/>
-      <c r="E30" s="68"/>
+      <c r="A30" s="64"/>
+      <c r="B30" s="64"/>
+      <c r="C30" s="64"/>
+      <c r="D30" s="64"/>
+      <c r="E30" s="64"/>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -10512,700 +10746,730 @@
   </cols>
   <sheetData>
     <row r="1" ht="54.75" customHeight="1">
-      <c r="A1" s="61" t="s">
-        <v>312</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="61" t="s">
-        <v>313</v>
-      </c>
-      <c r="D1" s="62"/>
-      <c r="E1" s="63" t="s">
+      <c r="A1" s="56" t="s">
+        <v>351</v>
+      </c>
+      <c r="B1" s="57"/>
+      <c r="C1" s="56" t="s">
+        <v>352</v>
+      </c>
+      <c r="D1" s="57"/>
+      <c r="E1" s="58" t="s">
+        <v>193</v>
+      </c>
+      <c r="F1" s="58" t="s">
+        <v>194</v>
+      </c>
+      <c r="G1" s="59"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="60" t="s">
+        <v>195</v>
+      </c>
+      <c r="B2" s="60" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="60" t="s">
+        <v>196</v>
+      </c>
+      <c r="D2" s="60" t="s">
+        <v>197</v>
+      </c>
+      <c r="E2" s="60" t="s">
+        <v>198</v>
+      </c>
+      <c r="F2" s="60" t="s">
+        <v>199</v>
+      </c>
+      <c r="G2" s="60" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="33" t="s">
+        <v>147</v>
+      </c>
+      <c r="B3" s="78" t="s">
+        <v>148</v>
+      </c>
+      <c r="C3" s="78" t="s">
+        <v>353</v>
+      </c>
+      <c r="D3" s="68" t="s">
+        <v>354</v>
+      </c>
+      <c r="E3" s="68" t="s">
+        <v>355</v>
+      </c>
+      <c r="F3" s="50" t="s">
+        <v>356</v>
+      </c>
+      <c r="G3" s="50" t="s">
+        <v>205</v>
+      </c>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="64"/>
+      <c r="L3" s="64"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="64"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="64"/>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="64"/>
+      <c r="V3" s="64"/>
+      <c r="W3" s="64"/>
+      <c r="X3" s="64"/>
+      <c r="Y3" s="64"/>
+      <c r="Z3" s="64"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="B4" s="61" t="s">
+        <v>357</v>
+      </c>
+      <c r="C4" s="78" t="s">
+        <v>358</v>
+      </c>
+      <c r="D4" s="68" t="s">
+        <v>359</v>
+      </c>
+      <c r="E4" s="68" t="s">
+        <v>360</v>
+      </c>
+      <c r="F4" s="50" t="s">
+        <v>361</v>
+      </c>
+      <c r="G4" s="50" t="s">
+        <v>205</v>
+      </c>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
+      <c r="K4" s="64"/>
+      <c r="L4" s="64"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="64"/>
+      <c r="W4" s="64"/>
+      <c r="X4" s="64"/>
+      <c r="Y4" s="64"/>
+      <c r="Z4" s="64"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="B5" s="61" t="s">
         <v>154</v>
       </c>
-      <c r="F1" s="63" t="s">
-        <v>155</v>
-      </c>
-      <c r="G1" s="64"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="65" t="s">
+      <c r="C5" s="78" t="s">
+        <v>362</v>
+      </c>
+      <c r="D5" s="68" t="s">
+        <v>363</v>
+      </c>
+      <c r="E5" s="68" t="s">
+        <v>364</v>
+      </c>
+      <c r="F5" s="50" t="s">
+        <v>365</v>
+      </c>
+      <c r="G5" s="50" t="s">
+        <v>205</v>
+      </c>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="64"/>
+      <c r="K5" s="64"/>
+      <c r="L5" s="64"/>
+      <c r="M5" s="64"/>
+      <c r="N5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="64"/>
+      <c r="Q5" s="64"/>
+      <c r="R5" s="64"/>
+      <c r="S5" s="64"/>
+      <c r="T5" s="64"/>
+      <c r="U5" s="64"/>
+      <c r="V5" s="64"/>
+      <c r="W5" s="64"/>
+      <c r="X5" s="64"/>
+      <c r="Y5" s="64"/>
+      <c r="Z5" s="64"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="33" t="s">
         <v>156</v>
       </c>
-      <c r="B2" s="65" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="65" t="s">
-        <v>157</v>
-      </c>
-      <c r="D2" s="65" t="s">
-        <v>158</v>
-      </c>
-      <c r="E2" s="65" t="s">
+      <c r="B6" s="61" t="s">
+        <v>366</v>
+      </c>
+      <c r="C6" s="78" t="s">
+        <v>367</v>
+      </c>
+      <c r="D6" s="68" t="s">
+        <v>368</v>
+      </c>
+      <c r="E6" s="69" t="s">
+        <v>369</v>
+      </c>
+      <c r="F6" s="72" t="s">
+        <v>370</v>
+      </c>
+      <c r="G6" s="50" t="s">
+        <v>205</v>
+      </c>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="64"/>
+      <c r="L6" s="64"/>
+      <c r="M6" s="64"/>
+      <c r="N6" s="64"/>
+      <c r="O6" s="64"/>
+      <c r="P6" s="64"/>
+      <c r="Q6" s="64"/>
+      <c r="R6" s="64"/>
+      <c r="S6" s="64"/>
+      <c r="T6" s="64"/>
+      <c r="U6" s="64"/>
+      <c r="V6" s="64"/>
+      <c r="W6" s="64"/>
+      <c r="X6" s="64"/>
+      <c r="Y6" s="64"/>
+      <c r="Z6" s="64"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="33" t="s">
         <v>159</v>
       </c>
-      <c r="F2" s="65" t="s">
-        <v>160</v>
-      </c>
-      <c r="G2" s="65" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="82"/>
-      <c r="B3" s="83" t="s">
-        <v>123</v>
-      </c>
-      <c r="C3" s="83" t="s">
-        <v>314</v>
-      </c>
-      <c r="D3" s="72" t="s">
-        <v>315</v>
-      </c>
-      <c r="E3" s="72" t="s">
-        <v>316</v>
-      </c>
-      <c r="F3" s="54" t="s">
-        <v>317</v>
-      </c>
-      <c r="G3" s="54" t="s">
-        <v>166</v>
-      </c>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="68"/>
-      <c r="O3" s="68"/>
-      <c r="P3" s="68"/>
-      <c r="Q3" s="68"/>
-      <c r="R3" s="68"/>
-      <c r="S3" s="68"/>
-      <c r="T3" s="68"/>
-      <c r="U3" s="68"/>
-      <c r="V3" s="68"/>
-      <c r="W3" s="68"/>
-      <c r="X3" s="68"/>
-      <c r="Y3" s="68"/>
-      <c r="Z3" s="68"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="82"/>
-      <c r="B4" s="37" t="s">
-        <v>318</v>
-      </c>
-      <c r="C4" s="83" t="s">
-        <v>319</v>
-      </c>
-      <c r="D4" s="72" t="s">
-        <v>320</v>
-      </c>
-      <c r="E4" s="72" t="s">
-        <v>321</v>
-      </c>
-      <c r="F4" s="54" t="s">
-        <v>322</v>
-      </c>
-      <c r="G4" s="54" t="s">
-        <v>166</v>
-      </c>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68"/>
-      <c r="L4" s="68"/>
-      <c r="M4" s="68"/>
-      <c r="N4" s="68"/>
-      <c r="O4" s="68"/>
-      <c r="P4" s="68"/>
-      <c r="Q4" s="68"/>
-      <c r="R4" s="68"/>
-      <c r="S4" s="68"/>
-      <c r="T4" s="68"/>
-      <c r="U4" s="68"/>
-      <c r="V4" s="68"/>
-      <c r="W4" s="68"/>
-      <c r="X4" s="68"/>
-      <c r="Y4" s="68"/>
-      <c r="Z4" s="68"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="82"/>
-      <c r="B5" s="37" t="s">
-        <v>127</v>
-      </c>
-      <c r="C5" s="83" t="s">
-        <v>323</v>
-      </c>
-      <c r="D5" s="72" t="s">
-        <v>324</v>
-      </c>
-      <c r="E5" s="72" t="s">
-        <v>325</v>
-      </c>
-      <c r="F5" s="54" t="s">
-        <v>326</v>
-      </c>
-      <c r="G5" s="54" t="s">
-        <v>166</v>
-      </c>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="68"/>
-      <c r="L5" s="68"/>
-      <c r="M5" s="68"/>
-      <c r="N5" s="68"/>
-      <c r="O5" s="68"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="68"/>
-      <c r="T5" s="68"/>
-      <c r="U5" s="68"/>
-      <c r="V5" s="68"/>
-      <c r="W5" s="68"/>
-      <c r="X5" s="68"/>
-      <c r="Y5" s="68"/>
-      <c r="Z5" s="68"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="82"/>
-      <c r="B6" s="37" t="s">
-        <v>327</v>
-      </c>
-      <c r="C6" s="83" t="s">
-        <v>328</v>
-      </c>
-      <c r="D6" s="72" t="s">
-        <v>329</v>
-      </c>
-      <c r="E6" s="73" t="s">
-        <v>330</v>
-      </c>
-      <c r="F6" s="76" t="s">
-        <v>331</v>
-      </c>
-      <c r="G6" s="54" t="s">
-        <v>166</v>
-      </c>
-      <c r="H6" s="68"/>
-      <c r="I6" s="68"/>
-      <c r="J6" s="68"/>
-      <c r="K6" s="68"/>
-      <c r="L6" s="68"/>
-      <c r="M6" s="68"/>
-      <c r="N6" s="68"/>
-      <c r="O6" s="68"/>
-      <c r="P6" s="68"/>
-      <c r="Q6" s="68"/>
-      <c r="R6" s="68"/>
-      <c r="S6" s="68"/>
-      <c r="T6" s="68"/>
-      <c r="U6" s="68"/>
-      <c r="V6" s="68"/>
-      <c r="W6" s="68"/>
-      <c r="X6" s="68"/>
-      <c r="Y6" s="68"/>
-      <c r="Z6" s="68"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="82"/>
-      <c r="B7" s="37" t="s">
-        <v>332</v>
-      </c>
-      <c r="C7" s="83" t="s">
-        <v>333</v>
-      </c>
-      <c r="D7" s="72" t="s">
-        <v>334</v>
-      </c>
-      <c r="E7" s="73" t="s">
-        <v>335</v>
-      </c>
-      <c r="F7" s="76" t="s">
-        <v>336</v>
-      </c>
-      <c r="G7" s="54" t="s">
-        <v>166</v>
-      </c>
-      <c r="H7" s="68"/>
-      <c r="I7" s="68"/>
-      <c r="J7" s="68"/>
-      <c r="K7" s="68"/>
-      <c r="L7" s="68"/>
-      <c r="M7" s="68"/>
-      <c r="N7" s="68"/>
-      <c r="O7" s="68"/>
-      <c r="P7" s="68"/>
-      <c r="Q7" s="68"/>
-      <c r="R7" s="68"/>
-      <c r="S7" s="68"/>
-      <c r="T7" s="68"/>
-      <c r="U7" s="68"/>
-      <c r="V7" s="68"/>
-      <c r="W7" s="68"/>
-      <c r="X7" s="68"/>
-      <c r="Y7" s="68"/>
-      <c r="Z7" s="68"/>
+      <c r="B7" s="61" t="s">
+        <v>371</v>
+      </c>
+      <c r="C7" s="78" t="s">
+        <v>372</v>
+      </c>
+      <c r="D7" s="68" t="s">
+        <v>373</v>
+      </c>
+      <c r="E7" s="69" t="s">
+        <v>374</v>
+      </c>
+      <c r="F7" s="72" t="s">
+        <v>375</v>
+      </c>
+      <c r="G7" s="50" t="s">
+        <v>205</v>
+      </c>
+      <c r="H7" s="64"/>
+      <c r="I7" s="64"/>
+      <c r="J7" s="64"/>
+      <c r="K7" s="64"/>
+      <c r="L7" s="64"/>
+      <c r="M7" s="64"/>
+      <c r="N7" s="64"/>
+      <c r="O7" s="64"/>
+      <c r="P7" s="64"/>
+      <c r="Q7" s="64"/>
+      <c r="R7" s="64"/>
+      <c r="S7" s="64"/>
+      <c r="T7" s="64"/>
+      <c r="U7" s="64"/>
+      <c r="V7" s="64"/>
+      <c r="W7" s="64"/>
+      <c r="X7" s="64"/>
+      <c r="Y7" s="64"/>
+      <c r="Z7" s="64"/>
     </row>
     <row r="8">
-      <c r="A8" s="82"/>
-      <c r="B8" s="37" t="s">
-        <v>76</v>
-      </c>
-      <c r="C8" s="83" t="s">
-        <v>337</v>
-      </c>
-      <c r="D8" s="72" t="s">
-        <v>338</v>
-      </c>
-      <c r="E8" s="73" t="s">
-        <v>339</v>
-      </c>
-      <c r="F8" s="76" t="s">
-        <v>340</v>
-      </c>
-      <c r="G8" s="54" t="s">
-        <v>166</v>
-      </c>
-      <c r="H8" s="68"/>
-      <c r="I8" s="68"/>
-      <c r="J8" s="68"/>
-      <c r="K8" s="68"/>
-      <c r="L8" s="68"/>
-      <c r="M8" s="68"/>
-      <c r="N8" s="68"/>
-      <c r="O8" s="68"/>
-      <c r="P8" s="68"/>
-      <c r="Q8" s="68"/>
-      <c r="R8" s="68"/>
-      <c r="S8" s="68"/>
-      <c r="T8" s="68"/>
-      <c r="U8" s="68"/>
-      <c r="V8" s="68"/>
-      <c r="W8" s="68"/>
-      <c r="X8" s="68"/>
-      <c r="Y8" s="68"/>
-      <c r="Z8" s="68"/>
+      <c r="A8" s="33" t="s">
+        <v>162</v>
+      </c>
+      <c r="B8" s="61" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="78" t="s">
+        <v>376</v>
+      </c>
+      <c r="D8" s="68" t="s">
+        <v>377</v>
+      </c>
+      <c r="E8" s="69" t="s">
+        <v>378</v>
+      </c>
+      <c r="F8" s="72" t="s">
+        <v>379</v>
+      </c>
+      <c r="G8" s="50" t="s">
+        <v>205</v>
+      </c>
+      <c r="H8" s="64"/>
+      <c r="I8" s="64"/>
+      <c r="J8" s="64"/>
+      <c r="K8" s="64"/>
+      <c r="L8" s="64"/>
+      <c r="M8" s="64"/>
+      <c r="N8" s="64"/>
+      <c r="O8" s="64"/>
+      <c r="P8" s="64"/>
+      <c r="Q8" s="64"/>
+      <c r="R8" s="64"/>
+      <c r="S8" s="64"/>
+      <c r="T8" s="64"/>
+      <c r="U8" s="64"/>
+      <c r="V8" s="64"/>
+      <c r="W8" s="64"/>
+      <c r="X8" s="64"/>
+      <c r="Y8" s="64"/>
+      <c r="Z8" s="64"/>
     </row>
     <row r="9">
-      <c r="A9" s="82"/>
-      <c r="B9" s="83" t="s">
-        <v>134</v>
-      </c>
-      <c r="C9" s="83" t="s">
-        <v>341</v>
-      </c>
-      <c r="D9" s="72" t="s">
-        <v>342</v>
-      </c>
-      <c r="E9" s="73" t="s">
-        <v>343</v>
-      </c>
-      <c r="F9" s="54" t="s">
-        <v>344</v>
-      </c>
-      <c r="G9" s="54" t="s">
-        <v>166</v>
-      </c>
-      <c r="H9" s="68"/>
-      <c r="I9" s="68"/>
-      <c r="J9" s="68"/>
-      <c r="K9" s="68"/>
-      <c r="L9" s="68"/>
-      <c r="M9" s="68"/>
-      <c r="N9" s="68"/>
-      <c r="O9" s="68"/>
-      <c r="P9" s="68"/>
-      <c r="Q9" s="68"/>
-      <c r="R9" s="68"/>
-      <c r="S9" s="68"/>
-      <c r="T9" s="68"/>
-      <c r="U9" s="68"/>
-      <c r="V9" s="68"/>
-      <c r="W9" s="68"/>
-      <c r="X9" s="68"/>
-      <c r="Y9" s="68"/>
-      <c r="Z9" s="68"/>
+      <c r="A9" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="B9" s="78" t="s">
+        <v>165</v>
+      </c>
+      <c r="C9" s="78" t="s">
+        <v>380</v>
+      </c>
+      <c r="D9" s="68" t="s">
+        <v>381</v>
+      </c>
+      <c r="E9" s="69" t="s">
+        <v>382</v>
+      </c>
+      <c r="F9" s="50" t="s">
+        <v>383</v>
+      </c>
+      <c r="G9" s="50" t="s">
+        <v>205</v>
+      </c>
+      <c r="H9" s="64"/>
+      <c r="I9" s="64"/>
+      <c r="J9" s="64"/>
+      <c r="K9" s="64"/>
+      <c r="L9" s="64"/>
+      <c r="M9" s="64"/>
+      <c r="N9" s="64"/>
+      <c r="O9" s="64"/>
+      <c r="P9" s="64"/>
+      <c r="Q9" s="64"/>
+      <c r="R9" s="64"/>
+      <c r="S9" s="64"/>
+      <c r="T9" s="64"/>
+      <c r="U9" s="64"/>
+      <c r="V9" s="64"/>
+      <c r="W9" s="64"/>
+      <c r="X9" s="64"/>
+      <c r="Y9" s="64"/>
+      <c r="Z9" s="64"/>
     </row>
     <row r="10">
-      <c r="A10" s="82"/>
-      <c r="B10" s="37" t="s">
-        <v>345</v>
-      </c>
-      <c r="C10" s="83" t="s">
-        <v>346</v>
-      </c>
-      <c r="D10" s="72" t="s">
-        <v>347</v>
-      </c>
-      <c r="E10" s="73" t="s">
-        <v>348</v>
-      </c>
-      <c r="F10" s="54" t="s">
-        <v>349</v>
-      </c>
-      <c r="G10" s="54" t="s">
-        <v>166</v>
-      </c>
-      <c r="H10" s="68"/>
-      <c r="I10" s="68"/>
-      <c r="J10" s="68"/>
-      <c r="K10" s="68"/>
-      <c r="L10" s="68"/>
-      <c r="M10" s="68"/>
-      <c r="N10" s="68"/>
-      <c r="O10" s="68"/>
-      <c r="P10" s="68"/>
-      <c r="Q10" s="68"/>
-      <c r="R10" s="68"/>
-      <c r="S10" s="68"/>
-      <c r="T10" s="68"/>
-      <c r="U10" s="68"/>
-      <c r="V10" s="68"/>
-      <c r="W10" s="68"/>
-      <c r="X10" s="68"/>
-      <c r="Y10" s="68"/>
-      <c r="Z10" s="68"/>
+      <c r="A10" s="33" t="s">
+        <v>167</v>
+      </c>
+      <c r="B10" s="61" t="s">
+        <v>384</v>
+      </c>
+      <c r="C10" s="78" t="s">
+        <v>385</v>
+      </c>
+      <c r="D10" s="68" t="s">
+        <v>386</v>
+      </c>
+      <c r="E10" s="69" t="s">
+        <v>387</v>
+      </c>
+      <c r="F10" s="50" t="s">
+        <v>388</v>
+      </c>
+      <c r="G10" s="50" t="s">
+        <v>205</v>
+      </c>
+      <c r="H10" s="64"/>
+      <c r="I10" s="64"/>
+      <c r="J10" s="64"/>
+      <c r="K10" s="64"/>
+      <c r="L10" s="64"/>
+      <c r="M10" s="64"/>
+      <c r="N10" s="64"/>
+      <c r="O10" s="64"/>
+      <c r="P10" s="64"/>
+      <c r="Q10" s="64"/>
+      <c r="R10" s="64"/>
+      <c r="S10" s="64"/>
+      <c r="T10" s="64"/>
+      <c r="U10" s="64"/>
+      <c r="V10" s="64"/>
+      <c r="W10" s="64"/>
+      <c r="X10" s="64"/>
+      <c r="Y10" s="64"/>
+      <c r="Z10" s="64"/>
     </row>
     <row r="11">
-      <c r="A11" s="82"/>
-      <c r="B11" s="83" t="s">
-        <v>138</v>
-      </c>
-      <c r="C11" s="83" t="s">
-        <v>350</v>
-      </c>
-      <c r="D11" s="72" t="s">
-        <v>351</v>
-      </c>
-      <c r="E11" s="73" t="s">
-        <v>352</v>
-      </c>
-      <c r="F11" s="76" t="s">
-        <v>353</v>
-      </c>
-      <c r="G11" s="54" t="s">
-        <v>166</v>
-      </c>
-      <c r="H11" s="68"/>
-      <c r="I11" s="68"/>
-      <c r="J11" s="68"/>
-      <c r="K11" s="68"/>
-      <c r="L11" s="68"/>
-      <c r="M11" s="68"/>
-      <c r="N11" s="68"/>
-      <c r="O11" s="68"/>
-      <c r="P11" s="68"/>
-      <c r="Q11" s="68"/>
-      <c r="R11" s="68"/>
-      <c r="S11" s="68"/>
-      <c r="T11" s="68"/>
-      <c r="U11" s="68"/>
-      <c r="V11" s="68"/>
-      <c r="W11" s="68"/>
-      <c r="X11" s="68"/>
-      <c r="Y11" s="68"/>
-      <c r="Z11" s="68"/>
+      <c r="A11" s="33" t="s">
+        <v>170</v>
+      </c>
+      <c r="B11" s="78" t="s">
+        <v>171</v>
+      </c>
+      <c r="C11" s="78" t="s">
+        <v>389</v>
+      </c>
+      <c r="D11" s="68" t="s">
+        <v>390</v>
+      </c>
+      <c r="E11" s="69" t="s">
+        <v>391</v>
+      </c>
+      <c r="F11" s="72" t="s">
+        <v>392</v>
+      </c>
+      <c r="G11" s="50" t="s">
+        <v>205</v>
+      </c>
+      <c r="H11" s="64"/>
+      <c r="I11" s="64"/>
+      <c r="J11" s="64"/>
+      <c r="K11" s="64"/>
+      <c r="L11" s="64"/>
+      <c r="M11" s="64"/>
+      <c r="N11" s="64"/>
+      <c r="O11" s="64"/>
+      <c r="P11" s="64"/>
+      <c r="Q11" s="64"/>
+      <c r="R11" s="64"/>
+      <c r="S11" s="64"/>
+      <c r="T11" s="64"/>
+      <c r="U11" s="64"/>
+      <c r="V11" s="64"/>
+      <c r="W11" s="64"/>
+      <c r="X11" s="64"/>
+      <c r="Y11" s="64"/>
+      <c r="Z11" s="64"/>
     </row>
     <row r="12">
-      <c r="A12" s="82"/>
-      <c r="B12" s="83" t="s">
-        <v>88</v>
-      </c>
-      <c r="C12" s="83" t="s">
-        <v>354</v>
-      </c>
-      <c r="D12" s="72" t="s">
-        <v>355</v>
-      </c>
-      <c r="E12" s="73" t="s">
-        <v>356</v>
-      </c>
-      <c r="F12" s="54" t="s">
-        <v>357</v>
-      </c>
-      <c r="G12" s="54" t="s">
-        <v>166</v>
-      </c>
-      <c r="H12" s="68"/>
-      <c r="I12" s="68"/>
-      <c r="J12" s="68"/>
-      <c r="K12" s="68"/>
-      <c r="L12" s="68"/>
-      <c r="M12" s="68"/>
-      <c r="N12" s="68"/>
-      <c r="O12" s="68"/>
-      <c r="P12" s="68"/>
-      <c r="Q12" s="68"/>
-      <c r="R12" s="68"/>
-      <c r="S12" s="68"/>
-      <c r="T12" s="68"/>
-      <c r="U12" s="68"/>
-      <c r="V12" s="68"/>
-      <c r="W12" s="68"/>
-      <c r="X12" s="68"/>
-      <c r="Y12" s="68"/>
-      <c r="Z12" s="68"/>
+      <c r="A12" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="B12" s="78" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" s="78" t="s">
+        <v>393</v>
+      </c>
+      <c r="D12" s="68" t="s">
+        <v>394</v>
+      </c>
+      <c r="E12" s="69" t="s">
+        <v>395</v>
+      </c>
+      <c r="F12" s="50" t="s">
+        <v>396</v>
+      </c>
+      <c r="G12" s="50" t="s">
+        <v>205</v>
+      </c>
+      <c r="H12" s="64"/>
+      <c r="I12" s="64"/>
+      <c r="J12" s="64"/>
+      <c r="K12" s="64"/>
+      <c r="L12" s="64"/>
+      <c r="M12" s="64"/>
+      <c r="N12" s="64"/>
+      <c r="O12" s="64"/>
+      <c r="P12" s="64"/>
+      <c r="Q12" s="64"/>
+      <c r="R12" s="64"/>
+      <c r="S12" s="64"/>
+      <c r="T12" s="64"/>
+      <c r="U12" s="64"/>
+      <c r="V12" s="64"/>
+      <c r="W12" s="64"/>
+      <c r="X12" s="64"/>
+      <c r="Y12" s="64"/>
+      <c r="Z12" s="64"/>
     </row>
     <row r="13">
-      <c r="A13" s="82"/>
-      <c r="B13" s="83" t="s">
-        <v>141</v>
-      </c>
-      <c r="C13" s="83" t="s">
-        <v>358</v>
-      </c>
-      <c r="D13" s="72" t="s">
-        <v>359</v>
-      </c>
-      <c r="E13" s="73" t="s">
-        <v>360</v>
-      </c>
-      <c r="F13" s="76" t="s">
-        <v>361</v>
-      </c>
-      <c r="G13" s="54" t="s">
-        <v>166</v>
-      </c>
-      <c r="H13" s="68"/>
-      <c r="I13" s="68"/>
-      <c r="J13" s="68"/>
-      <c r="K13" s="68"/>
-      <c r="L13" s="68"/>
-      <c r="M13" s="68"/>
-      <c r="N13" s="68"/>
-      <c r="O13" s="68"/>
-      <c r="P13" s="68"/>
-      <c r="Q13" s="68"/>
-      <c r="R13" s="68"/>
-      <c r="S13" s="68"/>
-      <c r="T13" s="68"/>
-      <c r="U13" s="68"/>
-      <c r="V13" s="68"/>
-      <c r="W13" s="68"/>
-      <c r="X13" s="68"/>
-      <c r="Y13" s="68"/>
-      <c r="Z13" s="68"/>
+      <c r="A13" s="33" t="s">
+        <v>175</v>
+      </c>
+      <c r="B13" s="78" t="s">
+        <v>176</v>
+      </c>
+      <c r="C13" s="78" t="s">
+        <v>397</v>
+      </c>
+      <c r="D13" s="68" t="s">
+        <v>398</v>
+      </c>
+      <c r="E13" s="69" t="s">
+        <v>399</v>
+      </c>
+      <c r="F13" s="72" t="s">
+        <v>400</v>
+      </c>
+      <c r="G13" s="50" t="s">
+        <v>205</v>
+      </c>
+      <c r="H13" s="64"/>
+      <c r="I13" s="64"/>
+      <c r="J13" s="64"/>
+      <c r="K13" s="64"/>
+      <c r="L13" s="64"/>
+      <c r="M13" s="64"/>
+      <c r="N13" s="64"/>
+      <c r="O13" s="64"/>
+      <c r="P13" s="64"/>
+      <c r="Q13" s="64"/>
+      <c r="R13" s="64"/>
+      <c r="S13" s="64"/>
+      <c r="T13" s="64"/>
+      <c r="U13" s="64"/>
+      <c r="V13" s="64"/>
+      <c r="W13" s="64"/>
+      <c r="X13" s="64"/>
+      <c r="Y13" s="64"/>
+      <c r="Z13" s="64"/>
     </row>
     <row r="14">
-      <c r="A14" s="82"/>
-      <c r="B14" s="37" t="s">
-        <v>362</v>
-      </c>
-      <c r="C14" s="83" t="s">
-        <v>363</v>
-      </c>
-      <c r="D14" s="72" t="s">
-        <v>364</v>
-      </c>
-      <c r="E14" s="73" t="s">
-        <v>365</v>
-      </c>
-      <c r="F14" s="76" t="s">
-        <v>366</v>
-      </c>
-      <c r="G14" s="54" t="s">
-        <v>166</v>
-      </c>
-      <c r="H14" s="68"/>
-      <c r="I14" s="68"/>
-      <c r="J14" s="68"/>
-      <c r="K14" s="68"/>
-      <c r="L14" s="68"/>
-      <c r="M14" s="68"/>
-      <c r="N14" s="68"/>
-      <c r="O14" s="68"/>
-      <c r="P14" s="68"/>
-      <c r="Q14" s="68"/>
-      <c r="R14" s="68"/>
-      <c r="S14" s="68"/>
-      <c r="T14" s="68"/>
-      <c r="U14" s="68"/>
-      <c r="V14" s="68"/>
-      <c r="W14" s="68"/>
-      <c r="X14" s="68"/>
-      <c r="Y14" s="68"/>
-      <c r="Z14" s="68"/>
+      <c r="A14" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B14" s="61" t="s">
+        <v>401</v>
+      </c>
+      <c r="C14" s="78" t="s">
+        <v>402</v>
+      </c>
+      <c r="D14" s="68" t="s">
+        <v>403</v>
+      </c>
+      <c r="E14" s="69" t="s">
+        <v>404</v>
+      </c>
+      <c r="F14" s="72" t="s">
+        <v>405</v>
+      </c>
+      <c r="G14" s="50" t="s">
+        <v>205</v>
+      </c>
+      <c r="H14" s="64"/>
+      <c r="I14" s="64"/>
+      <c r="J14" s="64"/>
+      <c r="K14" s="64"/>
+      <c r="L14" s="64"/>
+      <c r="M14" s="64"/>
+      <c r="N14" s="64"/>
+      <c r="O14" s="64"/>
+      <c r="P14" s="64"/>
+      <c r="Q14" s="64"/>
+      <c r="R14" s="64"/>
+      <c r="S14" s="64"/>
+      <c r="T14" s="64"/>
+      <c r="U14" s="64"/>
+      <c r="V14" s="64"/>
+      <c r="W14" s="64"/>
+      <c r="X14" s="64"/>
+      <c r="Y14" s="64"/>
+      <c r="Z14" s="64"/>
     </row>
     <row r="15">
-      <c r="A15" s="83"/>
-      <c r="B15" s="37" t="s">
-        <v>145</v>
-      </c>
-      <c r="C15" s="83" t="s">
-        <v>367</v>
-      </c>
-      <c r="D15" s="73" t="s">
-        <v>368</v>
-      </c>
-      <c r="E15" s="73" t="s">
-        <v>369</v>
-      </c>
-      <c r="F15" s="75" t="s">
-        <v>370</v>
-      </c>
-      <c r="G15" s="54" t="s">
-        <v>166</v>
-      </c>
-      <c r="H15" s="68"/>
-      <c r="I15" s="68"/>
-      <c r="J15" s="68"/>
-      <c r="K15" s="68"/>
-      <c r="L15" s="68"/>
-      <c r="M15" s="68"/>
-      <c r="N15" s="68"/>
-      <c r="O15" s="68"/>
-      <c r="P15" s="68"/>
-      <c r="Q15" s="68"/>
-      <c r="R15" s="68"/>
-      <c r="S15" s="68"/>
-      <c r="T15" s="68"/>
-      <c r="U15" s="68"/>
-      <c r="V15" s="68"/>
-      <c r="W15" s="68"/>
-      <c r="X15" s="68"/>
-      <c r="Y15" s="68"/>
-      <c r="Z15" s="68"/>
+      <c r="A15" s="33" t="s">
+        <v>181</v>
+      </c>
+      <c r="B15" s="61" t="s">
+        <v>182</v>
+      </c>
+      <c r="C15" s="78" t="s">
+        <v>406</v>
+      </c>
+      <c r="D15" s="69" t="s">
+        <v>407</v>
+      </c>
+      <c r="E15" s="69" t="s">
+        <v>408</v>
+      </c>
+      <c r="F15" s="71" t="s">
+        <v>409</v>
+      </c>
+      <c r="G15" s="50" t="s">
+        <v>205</v>
+      </c>
+      <c r="H15" s="64"/>
+      <c r="I15" s="64"/>
+      <c r="J15" s="64"/>
+      <c r="K15" s="64"/>
+      <c r="L15" s="64"/>
+      <c r="M15" s="64"/>
+      <c r="N15" s="64"/>
+      <c r="O15" s="64"/>
+      <c r="P15" s="64"/>
+      <c r="Q15" s="64"/>
+      <c r="R15" s="64"/>
+      <c r="S15" s="64"/>
+      <c r="T15" s="64"/>
+      <c r="U15" s="64"/>
+      <c r="V15" s="64"/>
+      <c r="W15" s="64"/>
+      <c r="X15" s="64"/>
+      <c r="Y15" s="64"/>
+      <c r="Z15" s="64"/>
     </row>
     <row r="16">
-      <c r="A16" s="83"/>
-      <c r="B16" s="37" t="s">
-        <v>147</v>
-      </c>
-      <c r="C16" s="83" t="s">
-        <v>371</v>
-      </c>
-      <c r="D16" s="73" t="s">
-        <v>372</v>
-      </c>
-      <c r="E16" s="73" t="s">
-        <v>373</v>
-      </c>
-      <c r="F16" s="75" t="s">
-        <v>374</v>
-      </c>
-      <c r="G16" s="54" t="s">
-        <v>166</v>
-      </c>
-      <c r="H16" s="68"/>
-      <c r="I16" s="68"/>
-      <c r="J16" s="68"/>
-      <c r="K16" s="68"/>
-      <c r="L16" s="68"/>
-      <c r="M16" s="68"/>
-      <c r="N16" s="68"/>
-      <c r="O16" s="68"/>
-      <c r="P16" s="68"/>
-      <c r="Q16" s="68"/>
-      <c r="R16" s="68"/>
-      <c r="S16" s="68"/>
-      <c r="T16" s="68"/>
-      <c r="U16" s="68"/>
-      <c r="V16" s="68"/>
-      <c r="W16" s="68"/>
-      <c r="X16" s="68"/>
-      <c r="Y16" s="68"/>
-      <c r="Z16" s="68"/>
+      <c r="A16" s="33" t="s">
+        <v>184</v>
+      </c>
+      <c r="B16" s="61" t="s">
+        <v>185</v>
+      </c>
+      <c r="C16" s="78" t="s">
+        <v>410</v>
+      </c>
+      <c r="D16" s="69" t="s">
+        <v>411</v>
+      </c>
+      <c r="E16" s="69" t="s">
+        <v>412</v>
+      </c>
+      <c r="F16" s="71" t="s">
+        <v>413</v>
+      </c>
+      <c r="G16" s="50" t="s">
+        <v>205</v>
+      </c>
+      <c r="H16" s="64"/>
+      <c r="I16" s="64"/>
+      <c r="J16" s="64"/>
+      <c r="K16" s="64"/>
+      <c r="L16" s="64"/>
+      <c r="M16" s="64"/>
+      <c r="N16" s="64"/>
+      <c r="O16" s="64"/>
+      <c r="P16" s="64"/>
+      <c r="Q16" s="64"/>
+      <c r="R16" s="64"/>
+      <c r="S16" s="64"/>
+      <c r="T16" s="64"/>
+      <c r="U16" s="64"/>
+      <c r="V16" s="64"/>
+      <c r="W16" s="64"/>
+      <c r="X16" s="64"/>
+      <c r="Y16" s="64"/>
+      <c r="Z16" s="64"/>
     </row>
     <row r="17">
-      <c r="A17" s="83"/>
-      <c r="B17" s="37" t="s">
-        <v>375</v>
-      </c>
-      <c r="C17" s="83" t="s">
-        <v>376</v>
-      </c>
-      <c r="D17" s="73" t="s">
-        <v>377</v>
-      </c>
-      <c r="E17" s="73" t="s">
-        <v>378</v>
-      </c>
-      <c r="F17" s="84" t="s">
-        <v>379</v>
-      </c>
-      <c r="G17" s="54" t="s">
-        <v>166</v>
-      </c>
-      <c r="H17" s="68"/>
-      <c r="I17" s="68"/>
-      <c r="J17" s="68"/>
-      <c r="K17" s="68"/>
-      <c r="L17" s="68"/>
-      <c r="M17" s="68"/>
-      <c r="N17" s="68"/>
-      <c r="O17" s="68"/>
-      <c r="P17" s="68"/>
-      <c r="Q17" s="68"/>
-      <c r="R17" s="68"/>
-      <c r="S17" s="68"/>
-      <c r="T17" s="68"/>
-      <c r="U17" s="68"/>
-      <c r="V17" s="68"/>
-      <c r="W17" s="68"/>
-      <c r="X17" s="68"/>
-      <c r="Y17" s="68"/>
-      <c r="Z17" s="68"/>
+      <c r="A17" s="33" t="s">
+        <v>187</v>
+      </c>
+      <c r="B17" s="61" t="s">
+        <v>414</v>
+      </c>
+      <c r="C17" s="78" t="s">
+        <v>415</v>
+      </c>
+      <c r="D17" s="69" t="s">
+        <v>416</v>
+      </c>
+      <c r="E17" s="69" t="s">
+        <v>417</v>
+      </c>
+      <c r="F17" s="79" t="s">
+        <v>418</v>
+      </c>
+      <c r="G17" s="50" t="s">
+        <v>205</v>
+      </c>
+      <c r="H17" s="64"/>
+      <c r="I17" s="64"/>
+      <c r="J17" s="64"/>
+      <c r="K17" s="64"/>
+      <c r="L17" s="64"/>
+      <c r="M17" s="64"/>
+      <c r="N17" s="64"/>
+      <c r="O17" s="64"/>
+      <c r="P17" s="64"/>
+      <c r="Q17" s="64"/>
+      <c r="R17" s="64"/>
+      <c r="S17" s="64"/>
+      <c r="T17" s="64"/>
+      <c r="U17" s="64"/>
+      <c r="V17" s="64"/>
+      <c r="W17" s="64"/>
+      <c r="X17" s="64"/>
+      <c r="Y17" s="64"/>
+      <c r="Z17" s="64"/>
     </row>
     <row r="18">
-      <c r="A18" s="83"/>
-      <c r="B18" s="83"/>
-      <c r="C18" s="83"/>
-      <c r="D18" s="73"/>
-      <c r="E18" s="73"/>
-      <c r="F18" s="73"/>
-      <c r="G18" s="73"/>
-      <c r="H18" s="68"/>
-      <c r="I18" s="68"/>
-      <c r="J18" s="68"/>
-      <c r="K18" s="68"/>
-      <c r="L18" s="68"/>
-      <c r="M18" s="68"/>
-      <c r="N18" s="68"/>
-      <c r="O18" s="68"/>
-      <c r="P18" s="68"/>
-      <c r="Q18" s="68"/>
-      <c r="R18" s="68"/>
-      <c r="S18" s="68"/>
-      <c r="T18" s="68"/>
-      <c r="U18" s="68"/>
-      <c r="V18" s="68"/>
-      <c r="W18" s="68"/>
-      <c r="X18" s="68"/>
-      <c r="Y18" s="68"/>
-      <c r="Z18" s="68"/>
+      <c r="A18" s="78"/>
+      <c r="B18" s="78"/>
+      <c r="C18" s="78"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="69"/>
+      <c r="F18" s="69"/>
+      <c r="G18" s="69"/>
+      <c r="H18" s="64"/>
+      <c r="I18" s="64"/>
+      <c r="J18" s="64"/>
+      <c r="K18" s="64"/>
+      <c r="L18" s="64"/>
+      <c r="M18" s="64"/>
+      <c r="N18" s="64"/>
+      <c r="O18" s="64"/>
+      <c r="P18" s="64"/>
+      <c r="Q18" s="64"/>
+      <c r="R18" s="64"/>
+      <c r="S18" s="64"/>
+      <c r="T18" s="64"/>
+      <c r="U18" s="64"/>
+      <c r="V18" s="64"/>
+      <c r="W18" s="64"/>
+      <c r="X18" s="64"/>
+      <c r="Y18" s="64"/>
+      <c r="Z18" s="64"/>
     </row>
     <row r="19">
-      <c r="A19" s="83"/>
-      <c r="B19" s="37"/>
-      <c r="C19" s="73"/>
-      <c r="D19" s="73"/>
-      <c r="E19" s="73"/>
-      <c r="F19" s="73"/>
-      <c r="G19" s="73"/>
-      <c r="H19" s="68"/>
-      <c r="I19" s="68"/>
-      <c r="J19" s="68"/>
-      <c r="K19" s="68"/>
-      <c r="L19" s="68"/>
-      <c r="M19" s="68"/>
-      <c r="N19" s="68"/>
-      <c r="O19" s="68"/>
-      <c r="P19" s="68"/>
-      <c r="Q19" s="68"/>
-      <c r="R19" s="68"/>
-      <c r="S19" s="68"/>
-      <c r="T19" s="68"/>
-      <c r="U19" s="68"/>
-      <c r="V19" s="68"/>
-      <c r="W19" s="68"/>
-      <c r="X19" s="68"/>
-      <c r="Y19" s="68"/>
-      <c r="Z19" s="68"/>
+      <c r="A19" s="78"/>
+      <c r="B19" s="61"/>
+      <c r="C19" s="69"/>
+      <c r="D19" s="69"/>
+      <c r="E19" s="69"/>
+      <c r="F19" s="69"/>
+      <c r="G19" s="69"/>
+      <c r="H19" s="64"/>
+      <c r="I19" s="64"/>
+      <c r="J19" s="64"/>
+      <c r="K19" s="64"/>
+      <c r="L19" s="64"/>
+      <c r="M19" s="64"/>
+      <c r="N19" s="64"/>
+      <c r="O19" s="64"/>
+      <c r="P19" s="64"/>
+      <c r="Q19" s="64"/>
+      <c r="R19" s="64"/>
+      <c r="S19" s="64"/>
+      <c r="T19" s="64"/>
+      <c r="U19" s="64"/>
+      <c r="V19" s="64"/>
+      <c r="W19" s="64"/>
+      <c r="X19" s="64"/>
+      <c r="Y19" s="64"/>
+      <c r="Z19" s="64"/>
     </row>
     <row r="20" ht="15.75" customHeight="1"/>
     <row r="21" ht="15.75" customHeight="1"/>
